--- a/data/Escenarios_Gx/elmo_data.xlsx
+++ b/data/Escenarios_Gx/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3C4188-D590-42D3-AA10-B5C089602DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DF3684-A80C-47C5-9EFB-91697773D3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="406">
   <si>
     <t>id</t>
   </si>
@@ -1254,6 +1254,9 @@
   </si>
   <si>
     <t>Bess</t>
+  </si>
+  <si>
+    <t>USD/anno/kW</t>
   </si>
 </sst>
 </file>
@@ -11731,7 +11734,7 @@
         <v>396</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -11750,10 +11753,18 @@
       <c r="C3" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3"/>
+      <c r="D3" s="3">
+        <v>653.4</v>
+      </c>
+      <c r="E3" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G3" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
@@ -11765,10 +11776,18 @@
       <c r="C4" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="3"/>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11842,12 +11861,24 @@
       <c r="B3" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Escenarios_Gx/elmo_data.xlsx
+++ b/data/Escenarios_Gx/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DF3684-A80C-47C5-9EFB-91697773D3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E564D34E-7D83-445E-8D5A-D8E51C412E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -3499,7 +3499,7 @@
         <v>215756</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -3522,7 +3522,7 @@
         <v>215756</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -3545,7 +3545,7 @@
         <v>215756</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="E5">
         <v>2</v>

--- a/data/Escenarios_Gx/elmo_data.xlsx
+++ b/data/Escenarios_Gx/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_Gx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E564D34E-7D83-445E-8D5A-D8E51C412E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9F8BF0-769A-48A5-90E8-FD6D62DA6E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -2137,36 +2137,36 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AD17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" style="21" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" style="21" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="21" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5546875" style="22" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="22" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" style="22" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.85546875" style="22" customWidth="1"/>
-    <col min="24" max="24" width="18.42578125" style="22" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="22" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.88671875" style="22" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.88671875" style="22" customWidth="1"/>
+    <col min="24" max="24" width="18.44140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
         <v>3</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29">
         <v>1</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="29">
         <v>2</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="29">
         <v>3</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
         <v>4</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="29">
         <v>5</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="29">
         <v>6</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="29">
         <v>7</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="29">
         <v>8</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="29">
         <v>9</v>
       </c>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AD11"/>
     </row>
-    <row r="12" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="29">
         <v>10</v>
       </c>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AD12"/>
     </row>
-    <row r="13" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="29">
         <v>11</v>
       </c>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AD13"/>
     </row>
-    <row r="14" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="29">
         <v>12</v>
       </c>
@@ -3422,9 +3422,9 @@
       </c>
       <c r="AD14"/>
     </row>
-    <row r="15" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3434,15 +3434,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3566,9 +3566,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3639,17 +3639,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H346"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
         <v>3</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="57">
         <v>0</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="58">
         <v>1</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58">
         <v>2</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="57">
         <v>3</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58">
         <v>4</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="58">
         <v>5</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="57">
         <v>6</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="58">
         <v>7</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58">
         <v>8</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="57">
         <v>9</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58">
         <v>10</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="58">
         <v>11</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58">
         <v>12</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="57">
         <v>13</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58">
         <v>14</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="58">
         <v>15</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="57">
         <v>16</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="58">
         <v>17</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58">
         <v>18</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="57">
         <v>19</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58">
         <v>20</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="58">
         <v>21</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58">
         <v>22</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="57">
         <v>23</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="58">
         <v>24</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="57">
         <v>25</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="58">
         <v>26</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="58">
         <v>27</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="57">
         <v>28</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="58">
         <v>29</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="58">
         <v>30</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="57">
         <v>31</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="58">
         <v>32</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="58">
         <v>33</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="57">
         <v>34</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="58">
         <v>35</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="58">
         <v>36</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="58">
         <v>37</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="57">
         <v>38</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="58">
         <v>39</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="58">
         <v>40</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="58">
         <v>41</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="58">
         <v>42</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="58">
         <v>43</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="58">
         <v>44</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="58">
         <v>45</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="58">
         <v>46</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="58">
         <v>47</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="58">
         <v>48</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="58">
         <v>49</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="58">
         <v>50</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="58">
         <v>51</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="58">
         <v>52</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="58">
         <v>53</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="58">
         <v>54</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="58">
         <v>55</v>
       </c>
@@ -5157,7 +5157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="58">
         <v>56</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="58">
         <v>57</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="58">
         <v>58</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="58">
         <v>59</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="58">
         <v>60</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="58">
         <v>61</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="58">
         <v>62</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="58">
         <v>63</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="58">
         <v>64</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="58">
         <v>65</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="58">
         <v>66</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="58">
         <v>67</v>
       </c>
@@ -5469,7 +5469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="58">
         <v>68</v>
       </c>
@@ -5495,7 +5495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="58">
         <v>69</v>
       </c>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="58">
         <v>70</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="58">
         <v>71</v>
       </c>
@@ -5573,7 +5573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="58">
         <v>72</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="58">
         <v>73</v>
       </c>
@@ -5625,7 +5625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="58">
         <v>74</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="58">
         <v>75</v>
       </c>
@@ -5677,7 +5677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="58">
         <v>76</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="58">
         <v>77</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="58">
         <v>78</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="58">
         <v>79</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="58">
         <v>80</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="58">
         <v>81</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="58">
         <v>82</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="58">
         <v>83</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="58">
         <v>84</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="58">
         <v>85</v>
       </c>
@@ -5937,7 +5937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="58">
         <v>86</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="58">
         <v>87</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="58">
         <v>88</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="58">
         <v>89</v>
       </c>
@@ -6041,7 +6041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="58">
         <v>90</v>
       </c>
@@ -6067,7 +6067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="58">
         <v>91</v>
       </c>
@@ -6093,7 +6093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="58">
         <v>92</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="58">
         <v>93</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="58">
         <v>94</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="58">
         <v>95</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="58">
         <v>96</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="58">
         <v>97</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="58">
         <v>98</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="58">
         <v>99</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="58">
         <v>100</v>
       </c>
@@ -6327,7 +6327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="58">
         <v>101</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="58">
         <v>102</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="58">
         <v>103</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="58">
         <v>104</v>
       </c>
@@ -6431,7 +6431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="58">
         <v>105</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="58">
         <v>106</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="58">
         <v>107</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="58">
         <v>108</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="58">
         <v>109</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="58">
         <v>110</v>
       </c>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="58">
         <v>111</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="58">
         <v>112</v>
       </c>
@@ -6639,7 +6639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="58">
         <v>113</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="58">
         <v>114</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="58">
         <v>115</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="58">
         <v>116</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="58">
         <v>117</v>
       </c>
@@ -6769,7 +6769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="58">
         <v>118</v>
       </c>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="58">
         <v>119</v>
       </c>
@@ -6821,7 +6821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="58">
         <v>120</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="58">
         <v>121</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="58">
         <v>122</v>
       </c>
@@ -6899,7 +6899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="58">
         <v>123</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="58">
         <v>124</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="58">
         <v>125</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="58">
         <v>126</v>
       </c>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="58">
         <v>127</v>
       </c>
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="58">
         <v>128</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="58">
         <v>129</v>
       </c>
@@ -7081,7 +7081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="58">
         <v>130</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="58">
         <v>131</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="58">
         <v>132</v>
       </c>
@@ -7159,7 +7159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="58">
         <v>133</v>
       </c>
@@ -7185,7 +7185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="58">
         <v>134</v>
       </c>
@@ -7211,7 +7211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="58">
         <v>135</v>
       </c>
@@ -7237,7 +7237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="58">
         <v>136</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="58">
         <v>137</v>
       </c>
@@ -7289,7 +7289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="58">
         <v>138</v>
       </c>
@@ -7315,7 +7315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="58">
         <v>139</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="58">
         <v>140</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="58">
         <v>141</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="58">
         <v>142</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="58">
         <v>143</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="58">
         <v>144</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="58">
         <v>145</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="58">
         <v>146</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="58">
         <v>147</v>
       </c>
@@ -7549,7 +7549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="58">
         <v>148</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="58">
         <v>149</v>
       </c>
@@ -7601,7 +7601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="58">
         <v>150</v>
       </c>
@@ -7627,7 +7627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="58">
         <v>151</v>
       </c>
@@ -7653,7 +7653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="58">
         <v>152</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="58">
         <v>153</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="58">
         <v>154</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="58">
         <v>155</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="58">
         <v>156</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="58">
         <v>157</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="58">
         <v>158</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="58">
         <v>159</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="58">
         <v>160</v>
       </c>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="58">
         <v>161</v>
       </c>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="58">
         <v>162</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="58">
         <v>163</v>
       </c>
@@ -7965,7 +7965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="58">
         <v>164</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="58">
         <v>165</v>
       </c>
@@ -8017,7 +8017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="58">
         <v>166</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="58">
         <v>167</v>
       </c>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="58">
         <v>168</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="58">
         <v>169</v>
       </c>
@@ -8121,7 +8121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="58">
         <v>170</v>
       </c>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="58">
         <v>171</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="58">
         <v>172</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="58">
         <v>173</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="58">
         <v>174</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="58">
         <v>175</v>
       </c>
@@ -8277,7 +8277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="58">
         <v>176</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="58">
         <v>177</v>
       </c>
@@ -8329,7 +8329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="58">
         <v>178</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="58">
         <v>179</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="58">
         <v>180</v>
       </c>
@@ -8407,7 +8407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="58">
         <v>181</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="58">
         <v>182</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="58">
         <v>183</v>
       </c>
@@ -8485,7 +8485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="58">
         <v>184</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="58">
         <v>185</v>
       </c>
@@ -8537,7 +8537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" s="58">
         <v>186</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" s="58">
         <v>187</v>
       </c>
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" s="58">
         <v>188</v>
       </c>
@@ -8615,7 +8615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" s="58">
         <v>189</v>
       </c>
@@ -8641,7 +8641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="58">
         <v>190</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="58">
         <v>191</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="58">
         <v>192</v>
       </c>
@@ -8719,7 +8719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="58">
         <v>193</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="58">
         <v>194</v>
       </c>
@@ -8771,7 +8771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="58">
         <v>195</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="58">
         <v>196</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="58">
         <v>197</v>
       </c>
@@ -8849,7 +8849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="58">
         <v>198</v>
       </c>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="58">
         <v>199</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="58">
         <v>200</v>
       </c>
@@ -8927,7 +8927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="58">
         <v>201</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="58">
         <v>202</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="58">
         <v>203</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="58">
         <v>204</v>
       </c>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="58">
         <v>205</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="58">
         <v>206</v>
       </c>
@@ -9083,7 +9083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="58">
         <v>207</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="58">
         <v>208</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="58">
         <v>209</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="58">
         <v>210</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="58">
         <v>211</v>
       </c>
@@ -9213,7 +9213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="58">
         <v>212</v>
       </c>
@@ -9239,7 +9239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="58">
         <v>213</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="58">
         <v>214</v>
       </c>
@@ -9291,7 +9291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="58">
         <v>215</v>
       </c>
@@ -9317,7 +9317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="58">
         <v>216</v>
       </c>
@@ -9343,7 +9343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="58">
         <v>217</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="58">
         <v>218</v>
       </c>
@@ -9395,7 +9395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" s="58">
         <v>219</v>
       </c>
@@ -9421,7 +9421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" s="58">
         <v>220</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" s="58">
         <v>221</v>
       </c>
@@ -9473,7 +9473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="58">
         <v>222</v>
       </c>
@@ -9499,7 +9499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" s="58">
         <v>223</v>
       </c>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" s="58">
         <v>224</v>
       </c>
@@ -9551,7 +9551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" s="58">
         <v>225</v>
       </c>
@@ -9577,7 +9577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" s="58">
         <v>226</v>
       </c>
@@ -9603,7 +9603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" s="58">
         <v>227</v>
       </c>
@@ -9629,7 +9629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" s="58">
         <v>228</v>
       </c>
@@ -9655,7 +9655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" s="58">
         <v>229</v>
       </c>
@@ -9681,7 +9681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" s="58">
         <v>230</v>
       </c>
@@ -9707,7 +9707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" s="58">
         <v>231</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" s="58">
         <v>232</v>
       </c>
@@ -9759,7 +9759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" s="58">
         <v>233</v>
       </c>
@@ -9785,7 +9785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" s="58">
         <v>234</v>
       </c>
@@ -9811,7 +9811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" s="58">
         <v>235</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" s="58">
         <v>236</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" s="58">
         <v>237</v>
       </c>
@@ -9889,7 +9889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" s="58">
         <v>238</v>
       </c>
@@ -9915,7 +9915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" s="58">
         <v>239</v>
       </c>
@@ -9941,7 +9941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" s="58">
         <v>240</v>
       </c>
@@ -9967,7 +9967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" s="58">
         <v>241</v>
       </c>
@@ -9993,7 +9993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" s="58">
         <v>242</v>
       </c>
@@ -10019,7 +10019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" s="58">
         <v>243</v>
       </c>
@@ -10045,7 +10045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" s="58">
         <v>244</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" s="58">
         <v>245</v>
       </c>
@@ -10097,7 +10097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" s="58">
         <v>246</v>
       </c>
@@ -10123,7 +10123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" s="58">
         <v>247</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" s="58">
         <v>248</v>
       </c>
@@ -10175,7 +10175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" s="58">
         <v>249</v>
       </c>
@@ -10201,7 +10201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" s="58">
         <v>250</v>
       </c>
@@ -10227,7 +10227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" s="58">
         <v>251</v>
       </c>
@@ -10253,7 +10253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" s="58">
         <v>252</v>
       </c>
@@ -10279,7 +10279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" s="58">
         <v>253</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" s="58">
         <v>254</v>
       </c>
@@ -10331,7 +10331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" s="58">
         <v>255</v>
       </c>
@@ -10357,7 +10357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="58">
         <v>256</v>
       </c>
@@ -10383,7 +10383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="58">
         <v>257</v>
       </c>
@@ -10409,7 +10409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" s="58">
         <v>258</v>
       </c>
@@ -10435,7 +10435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" s="58">
         <v>259</v>
       </c>
@@ -10461,7 +10461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" s="58">
         <v>260</v>
       </c>
@@ -10487,7 +10487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" s="58">
         <v>261</v>
       </c>
@@ -10513,7 +10513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" s="58">
         <v>262</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" s="58">
         <v>263</v>
       </c>
@@ -10565,7 +10565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" s="58">
         <v>264</v>
       </c>
@@ -10591,7 +10591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" s="58">
         <v>265</v>
       </c>
@@ -10617,7 +10617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" s="58">
         <v>266</v>
       </c>
@@ -10643,7 +10643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" s="58">
         <v>267</v>
       </c>
@@ -10669,7 +10669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" s="58">
         <v>268</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" s="58">
         <v>269</v>
       </c>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" s="58">
         <v>270</v>
       </c>
@@ -10747,7 +10747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" s="58">
         <v>271</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" s="58">
         <v>272</v>
       </c>
@@ -10799,7 +10799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" s="58">
         <v>273</v>
       </c>
@@ -10825,7 +10825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" s="58">
         <v>274</v>
       </c>
@@ -10851,7 +10851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" s="58">
         <v>275</v>
       </c>
@@ -10877,7 +10877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" s="58">
         <v>276</v>
       </c>
@@ -10903,7 +10903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" s="58">
         <v>277</v>
       </c>
@@ -10929,7 +10929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" s="58">
         <v>278</v>
       </c>
@@ -10955,7 +10955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" s="58">
         <v>279</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" s="58">
         <v>280</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" s="58">
         <v>281</v>
       </c>
@@ -11033,7 +11033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" s="58">
         <v>282</v>
       </c>
@@ -11059,7 +11059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" s="58">
         <v>283</v>
       </c>
@@ -11085,7 +11085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" s="58">
         <v>284</v>
       </c>
@@ -11111,7 +11111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" s="58">
         <v>285</v>
       </c>
@@ -11137,7 +11137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" s="58">
         <v>286</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" s="58">
         <v>287</v>
       </c>
@@ -11189,10 +11189,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" s="58"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" s="59"/>
       <c r="B292" s="69"/>
       <c r="C292" s="66"/>
@@ -11200,7 +11200,7 @@
       <c r="G292" s="39"/>
       <c r="H292" s="40"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" s="60"/>
       <c r="B293" s="69"/>
       <c r="C293" s="67"/>
@@ -11208,7 +11208,7 @@
       <c r="G293" s="35"/>
       <c r="H293" s="6"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" s="61"/>
       <c r="B294" s="69"/>
       <c r="C294" s="67"/>
@@ -11216,7 +11216,7 @@
       <c r="G294" s="35"/>
       <c r="H294" s="6"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" s="62"/>
       <c r="B295" s="69"/>
       <c r="C295" s="67"/>
@@ -11224,7 +11224,7 @@
       <c r="G295" s="35"/>
       <c r="H295" s="6"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" s="62"/>
       <c r="B296" s="69"/>
       <c r="C296" s="67"/>
@@ -11232,7 +11232,7 @@
       <c r="G296" s="35"/>
       <c r="H296" s="6"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" s="62"/>
       <c r="B297" s="69"/>
       <c r="C297" s="67"/>
@@ -11240,7 +11240,7 @@
       <c r="G297" s="35"/>
       <c r="H297" s="6"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" s="60"/>
       <c r="B298" s="69"/>
       <c r="C298" s="67"/>
@@ -11248,7 +11248,7 @@
       <c r="G298" s="35"/>
       <c r="H298" s="6"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" s="61"/>
       <c r="B299" s="69"/>
       <c r="C299" s="67"/>
@@ -11256,7 +11256,7 @@
       <c r="G299" s="35"/>
       <c r="H299" s="6"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" s="62"/>
       <c r="B300" s="69"/>
       <c r="C300" s="67"/>
@@ -11264,7 +11264,7 @@
       <c r="G300" s="35"/>
       <c r="H300" s="6"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" s="62"/>
       <c r="B301" s="69"/>
       <c r="C301" s="67"/>
@@ -11272,7 +11272,7 @@
       <c r="G301" s="35"/>
       <c r="H301" s="6"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" s="62"/>
       <c r="B302" s="69"/>
       <c r="C302" s="67"/>
@@ -11280,7 +11280,7 @@
       <c r="G302" s="35"/>
       <c r="H302" s="6"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" s="60"/>
       <c r="B303" s="69"/>
       <c r="C303" s="67"/>
@@ -11288,7 +11288,7 @@
       <c r="G303" s="35"/>
       <c r="H303" s="6"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" s="61"/>
       <c r="B304" s="69"/>
       <c r="C304" s="67"/>
@@ -11296,7 +11296,7 @@
       <c r="G304" s="35"/>
       <c r="H304" s="6"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" s="62"/>
       <c r="B305" s="69"/>
       <c r="C305" s="67"/>
@@ -11304,7 +11304,7 @@
       <c r="G305" s="35"/>
       <c r="H305" s="6"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" s="62"/>
       <c r="B306" s="69"/>
       <c r="C306" s="67"/>
@@ -11312,7 +11312,7 @@
       <c r="G306" s="35"/>
       <c r="H306" s="6"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" s="62"/>
       <c r="B307" s="69"/>
       <c r="C307" s="67"/>
@@ -11320,7 +11320,7 @@
       <c r="G307" s="35"/>
       <c r="H307" s="6"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" s="60"/>
       <c r="B308" s="69"/>
       <c r="C308" s="67"/>
@@ -11328,7 +11328,7 @@
       <c r="G308" s="35"/>
       <c r="H308" s="6"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" s="61"/>
       <c r="B309" s="69"/>
       <c r="C309" s="67"/>
@@ -11336,7 +11336,7 @@
       <c r="G309" s="35"/>
       <c r="H309" s="6"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" s="62"/>
       <c r="B310" s="69"/>
       <c r="C310" s="67"/>
@@ -11344,7 +11344,7 @@
       <c r="G310" s="35"/>
       <c r="H310" s="6"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" s="62"/>
       <c r="B311" s="69"/>
       <c r="C311" s="67"/>
@@ -11352,7 +11352,7 @@
       <c r="G311" s="35"/>
       <c r="H311" s="6"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" s="62"/>
       <c r="B312" s="69"/>
       <c r="C312" s="67"/>
@@ -11360,7 +11360,7 @@
       <c r="G312" s="35"/>
       <c r="H312" s="6"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" s="60"/>
       <c r="B313" s="69"/>
       <c r="C313" s="67"/>
@@ -11368,7 +11368,7 @@
       <c r="G313" s="35"/>
       <c r="H313" s="6"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" s="61"/>
       <c r="B314" s="69"/>
       <c r="C314" s="67"/>
@@ -11376,7 +11376,7 @@
       <c r="G314" s="35"/>
       <c r="H314" s="6"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" s="62"/>
       <c r="B315" s="69"/>
       <c r="C315" s="67"/>
@@ -11384,7 +11384,7 @@
       <c r="G315" s="35"/>
       <c r="H315" s="6"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" s="62"/>
       <c r="B316" s="69"/>
       <c r="C316" s="67"/>
@@ -11392,7 +11392,7 @@
       <c r="G316" s="35"/>
       <c r="H316" s="6"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" s="62"/>
       <c r="B317" s="69"/>
       <c r="C317" s="67"/>
@@ -11400,7 +11400,7 @@
       <c r="G317" s="35"/>
       <c r="H317" s="6"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" s="60"/>
       <c r="B318" s="69"/>
       <c r="C318" s="67"/>
@@ -11408,7 +11408,7 @@
       <c r="G318" s="35"/>
       <c r="H318" s="6"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" s="61"/>
       <c r="B319" s="69"/>
       <c r="C319" s="67"/>
@@ -11416,7 +11416,7 @@
       <c r="G319" s="35"/>
       <c r="H319" s="6"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" s="62"/>
       <c r="B320" s="69"/>
       <c r="C320" s="67"/>
@@ -11424,7 +11424,7 @@
       <c r="G320" s="35"/>
       <c r="H320" s="6"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" s="62"/>
       <c r="B321" s="69"/>
       <c r="C321" s="67"/>
@@ -11432,7 +11432,7 @@
       <c r="G321" s="35"/>
       <c r="H321" s="6"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" s="62"/>
       <c r="B322" s="69"/>
       <c r="C322" s="67"/>
@@ -11440,7 +11440,7 @@
       <c r="G322" s="35"/>
       <c r="H322" s="6"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" s="60"/>
       <c r="B323" s="69"/>
       <c r="C323" s="67"/>
@@ -11448,7 +11448,7 @@
       <c r="G323" s="35"/>
       <c r="H323" s="6"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" s="61"/>
       <c r="B324" s="69"/>
       <c r="C324" s="67"/>
@@ -11456,7 +11456,7 @@
       <c r="G324" s="35"/>
       <c r="H324" s="6"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" s="62"/>
       <c r="B325" s="69"/>
       <c r="C325" s="67"/>
@@ -11464,7 +11464,7 @@
       <c r="G325" s="35"/>
       <c r="H325" s="6"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326" s="62"/>
       <c r="B326" s="69"/>
       <c r="C326" s="67"/>
@@ -11472,7 +11472,7 @@
       <c r="G326" s="35"/>
       <c r="H326" s="6"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327" s="62"/>
       <c r="B327" s="69"/>
       <c r="C327" s="67"/>
@@ -11480,7 +11480,7 @@
       <c r="G327" s="35"/>
       <c r="H327" s="6"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328" s="60"/>
       <c r="B328" s="69"/>
       <c r="C328" s="67"/>
@@ -11488,7 +11488,7 @@
       <c r="G328" s="35"/>
       <c r="H328" s="6"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" s="61"/>
       <c r="B329" s="69"/>
       <c r="C329" s="67"/>
@@ -11496,7 +11496,7 @@
       <c r="G329" s="35"/>
       <c r="H329" s="6"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" s="62"/>
       <c r="B330" s="69"/>
       <c r="C330" s="67"/>
@@ -11504,7 +11504,7 @@
       <c r="G330" s="35"/>
       <c r="H330" s="6"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" s="62"/>
       <c r="B331" s="69"/>
       <c r="C331" s="67"/>
@@ -11512,7 +11512,7 @@
       <c r="G331" s="35"/>
       <c r="H331" s="6"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" s="62"/>
       <c r="B332" s="69"/>
       <c r="C332" s="67"/>
@@ -11520,7 +11520,7 @@
       <c r="G332" s="35"/>
       <c r="H332" s="6"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" s="60"/>
       <c r="B333" s="69"/>
       <c r="C333" s="67"/>
@@ -11528,7 +11528,7 @@
       <c r="G333" s="35"/>
       <c r="H333" s="6"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" s="61"/>
       <c r="B334" s="69"/>
       <c r="C334" s="67"/>
@@ -11536,7 +11536,7 @@
       <c r="G334" s="35"/>
       <c r="H334" s="6"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" s="62"/>
       <c r="B335" s="69"/>
       <c r="C335" s="67"/>
@@ -11544,7 +11544,7 @@
       <c r="G335" s="35"/>
       <c r="H335" s="6"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" s="62"/>
       <c r="B336" s="69"/>
       <c r="C336" s="67"/>
@@ -11552,7 +11552,7 @@
       <c r="G336" s="35"/>
       <c r="H336" s="6"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A337" s="62"/>
       <c r="B337" s="69"/>
       <c r="C337" s="67"/>
@@ -11560,7 +11560,7 @@
       <c r="G337" s="35"/>
       <c r="H337" s="6"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338" s="60"/>
       <c r="B338" s="69"/>
       <c r="C338" s="67"/>
@@ -11568,7 +11568,7 @@
       <c r="G338" s="35"/>
       <c r="H338" s="6"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339" s="61"/>
       <c r="B339" s="69"/>
       <c r="C339" s="67"/>
@@ -11576,7 +11576,7 @@
       <c r="G339" s="35"/>
       <c r="H339" s="6"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A340" s="62"/>
       <c r="B340" s="69"/>
       <c r="C340" s="67"/>
@@ -11584,7 +11584,7 @@
       <c r="G340" s="35"/>
       <c r="H340" s="6"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A341" s="62"/>
       <c r="B341" s="69"/>
       <c r="C341" s="67"/>
@@ -11592,7 +11592,7 @@
       <c r="G341" s="35"/>
       <c r="H341" s="6"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A342" s="62"/>
       <c r="B342" s="69"/>
       <c r="C342" s="67"/>
@@ -11600,7 +11600,7 @@
       <c r="G342" s="35"/>
       <c r="H342" s="6"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A343" s="60"/>
       <c r="B343" s="69"/>
       <c r="C343" s="67"/>
@@ -11608,7 +11608,7 @@
       <c r="G343" s="35"/>
       <c r="H343" s="6"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A344" s="61"/>
       <c r="B344" s="69"/>
       <c r="C344" s="67"/>
@@ -11616,7 +11616,7 @@
       <c r="G344" s="35"/>
       <c r="H344" s="6"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A345" s="62"/>
       <c r="B345" s="69"/>
       <c r="C345" s="67"/>
@@ -11624,7 +11624,7 @@
       <c r="G345" s="35"/>
       <c r="H345" s="6"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A346" s="62"/>
       <c r="B346" s="69"/>
       <c r="C346" s="67"/>
@@ -11644,14 +11644,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11662,7 +11662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -11673,7 +11673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -11692,12 +11692,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A14C44-D450-4CE6-A53B-AE526E523579}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11720,7 +11720,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -11743,7 +11743,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -11754,19 +11754,19 @@
         <v>399</v>
       </c>
       <c r="D3" s="3">
-        <v>653.4</v>
+        <v>30.8</v>
       </c>
       <c r="E3" s="4">
-        <v>8.5</v>
+        <v>6.9</v>
       </c>
       <c r="F3" s="4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -11777,16 +11777,16 @@
         <v>400</v>
       </c>
       <c r="D4" s="3">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="E4" s="4">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
       <c r="G4" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11797,12 +11797,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{608181A6-F701-489E-ABA1-A027ABB48641}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11828,7 +11828,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -11854,7 +11854,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -11862,22 +11862,22 @@
         <v>404</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>73350</v>
       </c>
       <c r="D3" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="E3" s="4">
         <v>0</v>
       </c>
       <c r="F3" s="4">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
   </sheetData>

--- a/data/Escenarios_Gx/elmo_data.xlsx
+++ b/data/Escenarios_Gx/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29E9979-17A5-4B4D-BD83-32814DBB4A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1228C2-4E65-4EDD-AEF5-8BAA87B9EE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -5371,7 +5371,7 @@
         <v>6.9</v>
       </c>
       <c r="F3" s="4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G3" s="3">
         <v>5</v>
@@ -5394,7 +5394,7 @@
         <v>21.6</v>
       </c>
       <c r="F4" s="4">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G4" s="3">
         <v>5</v>
@@ -5470,13 +5470,13 @@
         <v>196</v>
       </c>
       <c r="C3" s="4">
-        <v>73350</v>
+        <v>18308</v>
       </c>
       <c r="D3" s="3">
         <v>2900</v>
       </c>
       <c r="E3" s="4">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="F3" s="4">
         <v>0.98</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>4000</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/data/Escenarios_Gx/elmo_data.xlsx
+++ b/data/Escenarios_Gx/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA56A85-6201-472C-9CFF-F6F8D532228F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA11737F-8CD8-4FA5-9F94-3E9950CE3934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="193">
   <si>
     <t>id</t>
   </si>
@@ -227,9 +227,6 @@
     <t>0.95</t>
   </si>
   <si>
-    <t>swap_time</t>
-  </si>
-  <si>
     <t>LH518B_2</t>
   </si>
   <si>
@@ -572,18 +569,6 @@
     <t>p_max_ssee</t>
   </si>
   <si>
-    <t>max_batteries</t>
-  </si>
-  <si>
-    <t>battery_cost</t>
-  </si>
-  <si>
-    <t>charge_time</t>
-  </si>
-  <si>
-    <t>Battery_swap</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -630,6 +615,9 @@
   </si>
   <si>
     <t>Bess</t>
+  </si>
+  <si>
+    <t>electric</t>
   </si>
 </sst>
 </file>
@@ -1500,7 +1488,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -1530,7 +1518,7 @@
     <col min="28" max="28" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1618,14 +1606,8 @@
       <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
@@ -1713,31 +1695,25 @@
       <c r="AC2" t="s">
         <v>37</v>
       </c>
-      <c r="AD2" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="31">
         <v>1</v>
       </c>
       <c r="B3" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="38" t="s">
-        <v>161</v>
+      <c r="C3" t="s">
+        <v>160</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G3" s="9">
         <v>18</v>
@@ -1808,31 +1784,25 @@
       <c r="AC3" t="s">
         <v>61</v>
       </c>
-      <c r="AD3">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="AE3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="31">
         <v>2</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>161</v>
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
+        <v>160</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>52</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4" s="9">
         <v>18</v>
@@ -1903,31 +1873,25 @@
       <c r="AC4" t="s">
         <v>61</v>
       </c>
-      <c r="AD4">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="AE4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="31">
         <v>3</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>161</v>
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
+        <v>160</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5" s="9">
         <v>18</v>
@@ -1998,31 +1962,25 @@
       <c r="AC5" t="s">
         <v>61</v>
       </c>
-      <c r="AD5">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="AE5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="31">
         <v>4</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>161</v>
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>160</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6" s="9">
         <v>18</v>
@@ -2093,17 +2051,7 @@
       <c r="AC6" t="s">
         <v>61</v>
       </c>
-      <c r="AD6">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="AE6">
-        <f>AE3</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2112,40 +2060,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1" t="s">
         <v>162</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>163</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>164</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>165</v>
       </c>
-      <c r="F1" t="s">
-        <v>166</v>
-      </c>
       <c r="G1" t="s">
-        <v>177</v>
-      </c>
-      <c r="H1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2153,7 +2098,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -2162,38 +2107,32 @@
         <v>51</v>
       </c>
       <c r="F2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C3">
         <v>215756</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
         <v>1500</v>
       </c>
     </row>
@@ -2205,36 +2144,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" t="s">
         <v>170</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>171</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>172</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>173</v>
       </c>
-      <c r="F1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G1" t="s">
-        <v>178</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2242,7 +2175,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
@@ -2253,19 +2186,13 @@
       <c r="F2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C3">
         <v>42071</v>
@@ -2278,12 +2205,6 @@
       </c>
       <c r="F3">
         <v>5000</v>
-      </c>
-      <c r="G3">
-        <v>79000</v>
-      </c>
-      <c r="H3" t="s">
-        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2364,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" s="60" t="s">
         <v>6</v>
@@ -2390,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" s="60" t="s">
         <v>6</v>
@@ -2416,7 +2337,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="60" t="s">
         <v>6</v>
@@ -2442,7 +2363,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="60" t="s">
         <v>6</v>
@@ -2468,7 +2389,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="60" t="s">
         <v>6</v>
@@ -2494,7 +2415,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" s="60" t="s">
         <v>6</v>
@@ -2520,7 +2441,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" s="60" t="s">
         <v>6</v>
@@ -2546,7 +2467,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C10" s="60" t="s">
         <v>6</v>
@@ -2572,7 +2493,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" s="60" t="s">
         <v>6</v>
@@ -2598,7 +2519,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="60" t="s">
         <v>6</v>
@@ -2624,7 +2545,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C13" s="60" t="s">
         <v>6</v>
@@ -2650,7 +2571,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C14" s="60" t="s">
         <v>6</v>
@@ -2676,7 +2597,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="60" t="s">
         <v>6</v>
@@ -2702,7 +2623,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C16" s="60" t="s">
         <v>6</v>
@@ -2728,7 +2649,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C17" s="60" t="s">
         <v>6</v>
@@ -2754,7 +2675,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C18" s="60" t="s">
         <v>6</v>
@@ -2780,7 +2701,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="60" t="s">
         <v>6</v>
@@ -2806,7 +2727,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C20" s="60" t="s">
         <v>6</v>
@@ -2832,7 +2753,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C21" s="60" t="s">
         <v>6</v>
@@ -2858,7 +2779,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C22" s="60" t="s">
         <v>6</v>
@@ -2884,7 +2805,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C23" s="60" t="s">
         <v>6</v>
@@ -2910,7 +2831,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C24" s="60" t="s">
         <v>6</v>
@@ -2936,7 +2857,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C25" s="60" t="s">
         <v>6</v>
@@ -2962,7 +2883,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C26" s="60" t="s">
         <v>13</v>
@@ -2988,7 +2909,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C27" s="60" t="s">
         <v>13</v>
@@ -3014,7 +2935,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28" s="60" t="s">
         <v>13</v>
@@ -3040,7 +2961,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C29" s="60" t="s">
         <v>13</v>
@@ -3066,7 +2987,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C30" s="60" t="s">
         <v>13</v>
@@ -3092,7 +3013,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="60" t="s">
         <v>13</v>
@@ -3118,7 +3039,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C32" s="60" t="s">
         <v>13</v>
@@ -3144,7 +3065,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="48" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C33" s="60" t="s">
         <v>13</v>
@@ -3170,7 +3091,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C34" s="60" t="s">
         <v>13</v>
@@ -3196,7 +3117,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="48" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C35" s="60" t="s">
         <v>13</v>
@@ -3222,7 +3143,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C36" s="60" t="s">
         <v>13</v>
@@ -3248,7 +3169,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C37" s="60" t="s">
         <v>13</v>
@@ -3274,7 +3195,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C38" s="60" t="s">
         <v>13</v>
@@ -3300,7 +3221,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="48" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C39" s="60" t="s">
         <v>13</v>
@@ -3326,7 +3247,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C40" s="60" t="s">
         <v>13</v>
@@ -3352,7 +3273,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C41" s="60" t="s">
         <v>13</v>
@@ -3378,7 +3299,7 @@
         <v>39</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C42" s="60" t="s">
         <v>13</v>
@@ -3404,7 +3325,7 @@
         <v>40</v>
       </c>
       <c r="B43" s="48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C43" s="60" t="s">
         <v>13</v>
@@ -3430,7 +3351,7 @@
         <v>41</v>
       </c>
       <c r="B44" s="48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C44" s="60" t="s">
         <v>13</v>
@@ -3456,7 +3377,7 @@
         <v>42</v>
       </c>
       <c r="B45" s="48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C45" s="60" t="s">
         <v>13</v>
@@ -3482,7 +3403,7 @@
         <v>43</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C46" s="60" t="s">
         <v>13</v>
@@ -3508,7 +3429,7 @@
         <v>44</v>
       </c>
       <c r="B47" s="48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C47" s="60" t="s">
         <v>13</v>
@@ -3534,7 +3455,7 @@
         <v>45</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C48" s="60" t="s">
         <v>13</v>
@@ -3560,7 +3481,7 @@
         <v>46</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C49" s="60" t="s">
         <v>13</v>
@@ -3586,7 +3507,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C50" s="60" t="s">
         <v>14</v>
@@ -3612,7 +3533,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C51" s="60" t="s">
         <v>14</v>
@@ -3638,7 +3559,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C52" s="60" t="s">
         <v>14</v>
@@ -3664,7 +3585,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C53" s="60" t="s">
         <v>14</v>
@@ -3690,7 +3611,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C54" s="60" t="s">
         <v>14</v>
@@ -3716,7 +3637,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C55" s="60" t="s">
         <v>14</v>
@@ -3742,7 +3663,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C56" s="60" t="s">
         <v>14</v>
@@ -3768,7 +3689,7 @@
         <v>54</v>
       </c>
       <c r="B57" s="48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C57" s="60" t="s">
         <v>14</v>
@@ -3794,7 +3715,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C58" s="60" t="s">
         <v>14</v>
@@ -3820,7 +3741,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C59" s="60" t="s">
         <v>14</v>
@@ -3846,7 +3767,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C60" s="60" t="s">
         <v>14</v>
@@ -3872,7 +3793,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="48" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C61" s="60" t="s">
         <v>14</v>
@@ -3898,7 +3819,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="48" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C62" s="60" t="s">
         <v>14</v>
@@ -3924,7 +3845,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C63" s="60" t="s">
         <v>14</v>
@@ -3950,7 +3871,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C64" s="60" t="s">
         <v>14</v>
@@ -3976,7 +3897,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C65" s="60" t="s">
         <v>14</v>
@@ -4002,7 +3923,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="48" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C66" s="60" t="s">
         <v>14</v>
@@ -4028,7 +3949,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="48" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C67" s="60" t="s">
         <v>14</v>
@@ -4054,7 +3975,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C68" s="60" t="s">
         <v>14</v>
@@ -4080,7 +4001,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C69" s="60" t="s">
         <v>14</v>
@@ -4106,7 +4027,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="48" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C70" s="60" t="s">
         <v>14</v>
@@ -4132,7 +4053,7 @@
         <v>68</v>
       </c>
       <c r="B71" s="48" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C71" s="60" t="s">
         <v>14</v>
@@ -4158,7 +4079,7 @@
         <v>69</v>
       </c>
       <c r="B72" s="48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C72" s="60" t="s">
         <v>14</v>
@@ -4184,7 +4105,7 @@
         <v>70</v>
       </c>
       <c r="B73" s="48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C73" s="60" t="s">
         <v>14</v>
@@ -4210,7 +4131,7 @@
         <v>71</v>
       </c>
       <c r="B74" s="48" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C74" s="60" t="s">
         <v>15</v>
@@ -4236,7 +4157,7 @@
         <v>72</v>
       </c>
       <c r="B75" s="48" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C75" s="60" t="s">
         <v>15</v>
@@ -4262,7 +4183,7 @@
         <v>73</v>
       </c>
       <c r="B76" s="48" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C76" s="60" t="s">
         <v>15</v>
@@ -4288,7 +4209,7 @@
         <v>74</v>
       </c>
       <c r="B77" s="48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C77" s="60" t="s">
         <v>15</v>
@@ -4314,7 +4235,7 @@
         <v>75</v>
       </c>
       <c r="B78" s="48" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C78" s="60" t="s">
         <v>15</v>
@@ -4340,7 +4261,7 @@
         <v>76</v>
       </c>
       <c r="B79" s="48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C79" s="60" t="s">
         <v>15</v>
@@ -4366,7 +4287,7 @@
         <v>77</v>
       </c>
       <c r="B80" s="48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C80" s="60" t="s">
         <v>15</v>
@@ -4392,7 +4313,7 @@
         <v>78</v>
       </c>
       <c r="B81" s="48" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C81" s="60" t="s">
         <v>15</v>
@@ -4418,7 +4339,7 @@
         <v>79</v>
       </c>
       <c r="B82" s="48" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C82" s="60" t="s">
         <v>15</v>
@@ -4444,7 +4365,7 @@
         <v>80</v>
       </c>
       <c r="B83" s="48" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C83" s="60" t="s">
         <v>15</v>
@@ -4470,7 +4391,7 @@
         <v>81</v>
       </c>
       <c r="B84" s="48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C84" s="60" t="s">
         <v>15</v>
@@ -4496,7 +4417,7 @@
         <v>82</v>
       </c>
       <c r="B85" s="48" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C85" s="60" t="s">
         <v>15</v>
@@ -4522,7 +4443,7 @@
         <v>83</v>
       </c>
       <c r="B86" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C86" s="60" t="s">
         <v>15</v>
@@ -4548,7 +4469,7 @@
         <v>84</v>
       </c>
       <c r="B87" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C87" s="60" t="s">
         <v>15</v>
@@ -4574,7 +4495,7 @@
         <v>85</v>
       </c>
       <c r="B88" s="48" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C88" s="60" t="s">
         <v>15</v>
@@ -4600,7 +4521,7 @@
         <v>86</v>
       </c>
       <c r="B89" s="48" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C89" s="60" t="s">
         <v>15</v>
@@ -4626,7 +4547,7 @@
         <v>87</v>
       </c>
       <c r="B90" s="48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C90" s="60" t="s">
         <v>15</v>
@@ -4652,7 +4573,7 @@
         <v>88</v>
       </c>
       <c r="B91" s="48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C91" s="60" t="s">
         <v>15</v>
@@ -4678,7 +4599,7 @@
         <v>89</v>
       </c>
       <c r="B92" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C92" s="60" t="s">
         <v>15</v>
@@ -4704,7 +4625,7 @@
         <v>90</v>
       </c>
       <c r="B93" s="48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C93" s="60" t="s">
         <v>15</v>
@@ -4730,7 +4651,7 @@
         <v>91</v>
       </c>
       <c r="B94" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C94" s="60" t="s">
         <v>15</v>
@@ -4756,7 +4677,7 @@
         <v>92</v>
       </c>
       <c r="B95" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C95" s="60" t="s">
         <v>15</v>
@@ -4782,7 +4703,7 @@
         <v>93</v>
       </c>
       <c r="B96" s="48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C96" s="60" t="s">
         <v>15</v>
@@ -5316,19 +5237,19 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5342,10 +5263,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -5359,10 +5280,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D3" s="3">
         <v>30.8</v>
@@ -5382,10 +5303,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D4" s="3">
         <v>119</v>
@@ -5418,22 +5339,22 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -5444,10 +5365,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>34</v>
@@ -5467,7 +5388,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C3" s="4">
         <v>18308</v>

--- a/data/Escenarios_Gx/elmo_data.xlsx
+++ b/data/Escenarios_Gx/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_Gx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA11737F-8CD8-4FA5-9F94-3E9950CE3934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2B5433-D3BE-4139-B514-3FBC3CBAD4EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="193">
   <si>
     <t>id</t>
   </si>
@@ -527,24 +527,9 @@
     <t>station_name</t>
   </si>
   <si>
-    <t>station_cost</t>
-  </si>
-  <si>
-    <t>distance_to_dn</t>
-  </si>
-  <si>
-    <t>max_chargers</t>
-  </si>
-  <si>
-    <t>man_time</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
-    <t>h</t>
-  </si>
-  <si>
     <t>station_1</t>
   </si>
   <si>
@@ -618,6 +603,21 @@
   </si>
   <si>
     <t>electric</t>
+  </si>
+  <si>
+    <t>c_fixed</t>
+  </si>
+  <si>
+    <t>c_bays</t>
+  </si>
+  <si>
+    <t>c_charger_space</t>
+  </si>
+  <si>
+    <t>max_bays</t>
+  </si>
+  <si>
+    <t>max_chargers_per_bay</t>
   </si>
 </sst>
 </file>
@@ -1489,36 +1489,36 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" style="23" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" style="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" style="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="23" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5546875" style="24" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.85546875" style="24" customWidth="1"/>
-    <col min="24" max="24" width="18.42578125" style="24" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="24" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.88671875" style="24" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.88671875" style="24" customWidth="1"/>
+    <col min="24" max="24" width="18.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" s="31">
         <v>1</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>160</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>52</v>
@@ -1785,7 +1785,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" s="31">
         <v>2</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>160</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>52</v>
@@ -1874,7 +1874,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" s="31">
         <v>3</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>160</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>52</v>
@@ -1963,7 +1963,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" s="31">
         <v>4</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>160</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>52</v>
@@ -2060,14 +2060,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2075,22 +2078,25 @@
         <v>161</v>
       </c>
       <c r="C1" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="D1" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="E1" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="F1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="G1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+      <c r="H1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2098,41 +2104,47 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2" t="s">
         <v>51</v>
       </c>
-      <c r="F2" t="s">
-        <v>167</v>
-      </c>
       <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C3">
-        <v>215756</v>
+        <v>35722</v>
       </c>
       <c r="D3">
-        <v>168</v>
+        <v>38221</v>
       </c>
       <c r="E3">
+        <v>5733</v>
+      </c>
+      <c r="F3">
         <v>2</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <v>1500</v>
       </c>
     </row>
@@ -2145,29 +2157,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2175,7 +2187,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
@@ -2187,12 +2199,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C3">
         <v>42071</v>
@@ -2218,17 +2230,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H152"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.140625" style="69" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="49" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.109375" style="69" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -2254,7 +2266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="51" t="s">
         <v>3</v>
       </c>
@@ -2280,7 +2292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="52">
         <v>0</v>
       </c>
@@ -2306,7 +2318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53">
         <v>1</v>
       </c>
@@ -2332,7 +2344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53">
         <v>2</v>
       </c>
@@ -2358,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="52">
         <v>3</v>
       </c>
@@ -2384,7 +2396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="53">
         <v>4</v>
       </c>
@@ -2410,7 +2422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="53">
         <v>5</v>
       </c>
@@ -2436,7 +2448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52">
         <v>6</v>
       </c>
@@ -2462,7 +2474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="53">
         <v>7</v>
       </c>
@@ -2488,7 +2500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="53">
         <v>8</v>
       </c>
@@ -2514,7 +2526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="52">
         <v>9</v>
       </c>
@@ -2540,7 +2552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="53">
         <v>10</v>
       </c>
@@ -2566,7 +2578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="53">
         <v>11</v>
       </c>
@@ -2592,7 +2604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="53">
         <v>12</v>
       </c>
@@ -2618,7 +2630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="52">
         <v>13</v>
       </c>
@@ -2644,7 +2656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="53">
         <v>14</v>
       </c>
@@ -2670,7 +2682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="53">
         <v>15</v>
       </c>
@@ -2696,7 +2708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="52">
         <v>16</v>
       </c>
@@ -2722,7 +2734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="53">
         <v>17</v>
       </c>
@@ -2748,7 +2760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="53">
         <v>18</v>
       </c>
@@ -2774,7 +2786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="52">
         <v>19</v>
       </c>
@@ -2800,7 +2812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="53">
         <v>20</v>
       </c>
@@ -2826,7 +2838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="53">
         <v>21</v>
       </c>
@@ -2852,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="53">
         <v>22</v>
       </c>
@@ -2878,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="52">
         <v>23</v>
       </c>
@@ -2904,7 +2916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="53">
         <v>24</v>
       </c>
@@ -2930,7 +2942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="52">
         <v>25</v>
       </c>
@@ -2956,7 +2968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="53">
         <v>26</v>
       </c>
@@ -2982,7 +2994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="53">
         <v>27</v>
       </c>
@@ -3008,7 +3020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="52">
         <v>28</v>
       </c>
@@ -3034,7 +3046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="53">
         <v>29</v>
       </c>
@@ -3060,7 +3072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="53">
         <v>30</v>
       </c>
@@ -3086,7 +3098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="52">
         <v>31</v>
       </c>
@@ -3112,7 +3124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="53">
         <v>32</v>
       </c>
@@ -3138,7 +3150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <v>33</v>
       </c>
@@ -3164,7 +3176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="52">
         <v>34</v>
       </c>
@@ -3190,7 +3202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="53">
         <v>35</v>
       </c>
@@ -3216,7 +3228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="53">
         <v>36</v>
       </c>
@@ -3242,7 +3254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <v>37</v>
       </c>
@@ -3268,7 +3280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="52">
         <v>38</v>
       </c>
@@ -3294,7 +3306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="53">
         <v>39</v>
       </c>
@@ -3320,7 +3332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="53">
         <v>40</v>
       </c>
@@ -3346,7 +3358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="53">
         <v>41</v>
       </c>
@@ -3372,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="53">
         <v>42</v>
       </c>
@@ -3398,7 +3410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="53">
         <v>43</v>
       </c>
@@ -3424,7 +3436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="53">
         <v>44</v>
       </c>
@@ -3450,7 +3462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="53">
         <v>45</v>
       </c>
@@ -3476,7 +3488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="53">
         <v>46</v>
       </c>
@@ -3502,7 +3514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="53">
         <v>47</v>
       </c>
@@ -3528,7 +3540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="53">
         <v>48</v>
       </c>
@@ -3554,7 +3566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="53">
         <v>49</v>
       </c>
@@ -3580,7 +3592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="53">
         <v>50</v>
       </c>
@@ -3606,7 +3618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="53">
         <v>51</v>
       </c>
@@ -3632,7 +3644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="53">
         <v>52</v>
       </c>
@@ -3658,7 +3670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="53">
         <v>53</v>
       </c>
@@ -3684,7 +3696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="53">
         <v>54</v>
       </c>
@@ -3710,7 +3722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="53">
         <v>55</v>
       </c>
@@ -3736,7 +3748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="53">
         <v>56</v>
       </c>
@@ -3762,7 +3774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="53">
         <v>57</v>
       </c>
@@ -3788,7 +3800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="53">
         <v>58</v>
       </c>
@@ -3814,7 +3826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="53">
         <v>59</v>
       </c>
@@ -3840,7 +3852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="53">
         <v>60</v>
       </c>
@@ -3866,7 +3878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="53">
         <v>61</v>
       </c>
@@ -3892,7 +3904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="53">
         <v>62</v>
       </c>
@@ -3918,7 +3930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="53">
         <v>63</v>
       </c>
@@ -3944,7 +3956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="53">
         <v>64</v>
       </c>
@@ -3970,7 +3982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="53">
         <v>65</v>
       </c>
@@ -3996,7 +4008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="53">
         <v>66</v>
       </c>
@@ -4022,7 +4034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="53">
         <v>67</v>
       </c>
@@ -4048,7 +4060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="53">
         <v>68</v>
       </c>
@@ -4074,7 +4086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="53">
         <v>69</v>
       </c>
@@ -4100,7 +4112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="53">
         <v>70</v>
       </c>
@@ -4126,7 +4138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="53">
         <v>71</v>
       </c>
@@ -4152,7 +4164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="53">
         <v>72</v>
       </c>
@@ -4178,7 +4190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="53">
         <v>73</v>
       </c>
@@ -4204,7 +4216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="53">
         <v>74</v>
       </c>
@@ -4230,7 +4242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="53">
         <v>75</v>
       </c>
@@ -4256,7 +4268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="53">
         <v>76</v>
       </c>
@@ -4282,7 +4294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="53">
         <v>77</v>
       </c>
@@ -4308,7 +4320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="53">
         <v>78</v>
       </c>
@@ -4334,7 +4346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="53">
         <v>79</v>
       </c>
@@ -4360,7 +4372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="53">
         <v>80</v>
       </c>
@@ -4386,7 +4398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="53">
         <v>81</v>
       </c>
@@ -4412,7 +4424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="53">
         <v>82</v>
       </c>
@@ -4438,7 +4450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="53">
         <v>83</v>
       </c>
@@ -4464,7 +4476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="53">
         <v>84</v>
       </c>
@@ -4490,7 +4502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="53">
         <v>85</v>
       </c>
@@ -4516,7 +4528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="53">
         <v>86</v>
       </c>
@@ -4542,7 +4554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="53">
         <v>87</v>
       </c>
@@ -4568,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="53">
         <v>88</v>
       </c>
@@ -4594,7 +4606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="53">
         <v>89</v>
       </c>
@@ -4620,7 +4632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="53">
         <v>90</v>
       </c>
@@ -4646,7 +4658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="53">
         <v>91</v>
       </c>
@@ -4672,7 +4684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="53">
         <v>92</v>
       </c>
@@ -4698,7 +4710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="53">
         <v>93</v>
       </c>
@@ -4724,10 +4736,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="54"/>
       <c r="B98" s="64"/>
       <c r="C98" s="61"/>
@@ -4735,7 +4747,7 @@
       <c r="G98" s="43"/>
       <c r="H98" s="44"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="55"/>
       <c r="B99" s="64"/>
       <c r="C99" s="62"/>
@@ -4743,7 +4755,7 @@
       <c r="G99" s="37"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="56"/>
       <c r="B100" s="64"/>
       <c r="C100" s="62"/>
@@ -4751,7 +4763,7 @@
       <c r="G100" s="37"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="57"/>
       <c r="B101" s="64"/>
       <c r="C101" s="62"/>
@@ -4759,7 +4771,7 @@
       <c r="G101" s="37"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="57"/>
       <c r="B102" s="64"/>
       <c r="C102" s="62"/>
@@ -4767,7 +4779,7 @@
       <c r="G102" s="37"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="57"/>
       <c r="B103" s="64"/>
       <c r="C103" s="62"/>
@@ -4775,7 +4787,7 @@
       <c r="G103" s="37"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="55"/>
       <c r="B104" s="64"/>
       <c r="C104" s="62"/>
@@ -4783,7 +4795,7 @@
       <c r="G104" s="37"/>
       <c r="H104" s="8"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="56"/>
       <c r="B105" s="64"/>
       <c r="C105" s="62"/>
@@ -4791,7 +4803,7 @@
       <c r="G105" s="37"/>
       <c r="H105" s="8"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="57"/>
       <c r="B106" s="64"/>
       <c r="C106" s="62"/>
@@ -4799,7 +4811,7 @@
       <c r="G106" s="37"/>
       <c r="H106" s="8"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="57"/>
       <c r="B107" s="64"/>
       <c r="C107" s="62"/>
@@ -4807,7 +4819,7 @@
       <c r="G107" s="37"/>
       <c r="H107" s="8"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="57"/>
       <c r="B108" s="64"/>
       <c r="C108" s="62"/>
@@ -4815,7 +4827,7 @@
       <c r="G108" s="37"/>
       <c r="H108" s="8"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="55"/>
       <c r="B109" s="64"/>
       <c r="C109" s="62"/>
@@ -4823,7 +4835,7 @@
       <c r="G109" s="37"/>
       <c r="H109" s="8"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="56"/>
       <c r="B110" s="64"/>
       <c r="C110" s="62"/>
@@ -4831,7 +4843,7 @@
       <c r="G110" s="37"/>
       <c r="H110" s="8"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="57"/>
       <c r="B111" s="64"/>
       <c r="C111" s="62"/>
@@ -4839,7 +4851,7 @@
       <c r="G111" s="37"/>
       <c r="H111" s="8"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="57"/>
       <c r="B112" s="64"/>
       <c r="C112" s="62"/>
@@ -4847,7 +4859,7 @@
       <c r="G112" s="37"/>
       <c r="H112" s="8"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="57"/>
       <c r="B113" s="64"/>
       <c r="C113" s="62"/>
@@ -4855,7 +4867,7 @@
       <c r="G113" s="37"/>
       <c r="H113" s="8"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="55"/>
       <c r="B114" s="64"/>
       <c r="C114" s="62"/>
@@ -4863,7 +4875,7 @@
       <c r="G114" s="37"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="56"/>
       <c r="B115" s="64"/>
       <c r="C115" s="62"/>
@@ -4871,7 +4883,7 @@
       <c r="G115" s="37"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="57"/>
       <c r="B116" s="64"/>
       <c r="C116" s="62"/>
@@ -4879,7 +4891,7 @@
       <c r="G116" s="37"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="57"/>
       <c r="B117" s="64"/>
       <c r="C117" s="62"/>
@@ -4887,7 +4899,7 @@
       <c r="G117" s="37"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="57"/>
       <c r="B118" s="64"/>
       <c r="C118" s="62"/>
@@ -4895,7 +4907,7 @@
       <c r="G118" s="37"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="55"/>
       <c r="B119" s="64"/>
       <c r="C119" s="62"/>
@@ -4903,7 +4915,7 @@
       <c r="G119" s="37"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="56"/>
       <c r="B120" s="64"/>
       <c r="C120" s="62"/>
@@ -4911,7 +4923,7 @@
       <c r="G120" s="37"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="57"/>
       <c r="B121" s="64"/>
       <c r="C121" s="62"/>
@@ -4919,7 +4931,7 @@
       <c r="G121" s="37"/>
       <c r="H121" s="8"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="57"/>
       <c r="B122" s="64"/>
       <c r="C122" s="62"/>
@@ -4927,7 +4939,7 @@
       <c r="G122" s="37"/>
       <c r="H122" s="8"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="57"/>
       <c r="B123" s="64"/>
       <c r="C123" s="62"/>
@@ -4935,7 +4947,7 @@
       <c r="G123" s="37"/>
       <c r="H123" s="8"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="55"/>
       <c r="B124" s="64"/>
       <c r="C124" s="62"/>
@@ -4943,7 +4955,7 @@
       <c r="G124" s="37"/>
       <c r="H124" s="8"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="56"/>
       <c r="B125" s="64"/>
       <c r="C125" s="62"/>
@@ -4951,7 +4963,7 @@
       <c r="G125" s="37"/>
       <c r="H125" s="8"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="57"/>
       <c r="B126" s="64"/>
       <c r="C126" s="62"/>
@@ -4959,7 +4971,7 @@
       <c r="G126" s="37"/>
       <c r="H126" s="8"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="57"/>
       <c r="B127" s="64"/>
       <c r="C127" s="62"/>
@@ -4967,7 +4979,7 @@
       <c r="G127" s="37"/>
       <c r="H127" s="8"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="57"/>
       <c r="B128" s="64"/>
       <c r="C128" s="62"/>
@@ -4975,7 +4987,7 @@
       <c r="G128" s="37"/>
       <c r="H128" s="8"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="55"/>
       <c r="B129" s="64"/>
       <c r="C129" s="62"/>
@@ -4983,7 +4995,7 @@
       <c r="G129" s="37"/>
       <c r="H129" s="8"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="56"/>
       <c r="B130" s="64"/>
       <c r="C130" s="62"/>
@@ -4991,7 +5003,7 @@
       <c r="G130" s="37"/>
       <c r="H130" s="8"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="57"/>
       <c r="B131" s="64"/>
       <c r="C131" s="62"/>
@@ -4999,7 +5011,7 @@
       <c r="G131" s="37"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="57"/>
       <c r="B132" s="64"/>
       <c r="C132" s="62"/>
@@ -5007,7 +5019,7 @@
       <c r="G132" s="37"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="57"/>
       <c r="B133" s="64"/>
       <c r="C133" s="62"/>
@@ -5015,7 +5027,7 @@
       <c r="G133" s="37"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="55"/>
       <c r="B134" s="64"/>
       <c r="C134" s="62"/>
@@ -5023,7 +5035,7 @@
       <c r="G134" s="37"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="56"/>
       <c r="B135" s="64"/>
       <c r="C135" s="62"/>
@@ -5031,7 +5043,7 @@
       <c r="G135" s="37"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="57"/>
       <c r="B136" s="64"/>
       <c r="C136" s="62"/>
@@ -5039,7 +5051,7 @@
       <c r="G136" s="37"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="57"/>
       <c r="B137" s="64"/>
       <c r="C137" s="62"/>
@@ -5047,7 +5059,7 @@
       <c r="G137" s="37"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="57"/>
       <c r="B138" s="64"/>
       <c r="C138" s="62"/>
@@ -5055,7 +5067,7 @@
       <c r="G138" s="37"/>
       <c r="H138" s="8"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="55"/>
       <c r="B139" s="64"/>
       <c r="C139" s="62"/>
@@ -5063,7 +5075,7 @@
       <c r="G139" s="37"/>
       <c r="H139" s="8"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="56"/>
       <c r="B140" s="64"/>
       <c r="C140" s="62"/>
@@ -5071,7 +5083,7 @@
       <c r="G140" s="37"/>
       <c r="H140" s="8"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="57"/>
       <c r="B141" s="64"/>
       <c r="C141" s="62"/>
@@ -5079,7 +5091,7 @@
       <c r="G141" s="37"/>
       <c r="H141" s="8"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="57"/>
       <c r="B142" s="64"/>
       <c r="C142" s="62"/>
@@ -5087,7 +5099,7 @@
       <c r="G142" s="37"/>
       <c r="H142" s="8"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="57"/>
       <c r="B143" s="64"/>
       <c r="C143" s="62"/>
@@ -5095,7 +5107,7 @@
       <c r="G143" s="37"/>
       <c r="H143" s="8"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="55"/>
       <c r="B144" s="64"/>
       <c r="C144" s="62"/>
@@ -5103,7 +5115,7 @@
       <c r="G144" s="37"/>
       <c r="H144" s="8"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="56"/>
       <c r="B145" s="64"/>
       <c r="C145" s="62"/>
@@ -5111,7 +5123,7 @@
       <c r="G145" s="37"/>
       <c r="H145" s="8"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="57"/>
       <c r="B146" s="64"/>
       <c r="C146" s="62"/>
@@ -5119,7 +5131,7 @@
       <c r="G146" s="37"/>
       <c r="H146" s="8"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="57"/>
       <c r="B147" s="64"/>
       <c r="C147" s="62"/>
@@ -5127,7 +5139,7 @@
       <c r="G147" s="37"/>
       <c r="H147" s="8"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="57"/>
       <c r="B148" s="64"/>
       <c r="C148" s="62"/>
@@ -5135,7 +5147,7 @@
       <c r="G148" s="37"/>
       <c r="H148" s="8"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="55"/>
       <c r="B149" s="64"/>
       <c r="C149" s="62"/>
@@ -5143,7 +5155,7 @@
       <c r="G149" s="37"/>
       <c r="H149" s="8"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="56"/>
       <c r="B150" s="64"/>
       <c r="C150" s="62"/>
@@ -5151,7 +5163,7 @@
       <c r="G150" s="37"/>
       <c r="H150" s="8"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="57"/>
       <c r="B151" s="64"/>
       <c r="C151" s="62"/>
@@ -5159,7 +5171,7 @@
       <c r="G151" s="37"/>
       <c r="H151" s="8"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="57"/>
       <c r="B152" s="64"/>
       <c r="C152" s="62"/>
@@ -5179,14 +5191,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5197,7 +5209,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5208,7 +5220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -5227,9 +5239,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C903B846-9155-4C37-ABE1-59FA4D45CD76}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5237,22 +5249,22 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5263,10 +5275,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -5275,15 +5287,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D3" s="3">
         <v>30.8</v>
@@ -5298,15 +5310,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D4" s="3">
         <v>119</v>
@@ -5329,9 +5341,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387AF5AC-D97C-4B95-B84B-AE3277E9ED2E}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5339,25 +5351,25 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5365,10 +5377,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>34</v>
@@ -5383,12 +5395,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C3" s="4">
         <v>18308</v>

--- a/data/Escenarios_Gx/elmo_data.xlsx
+++ b/data/Escenarios_Gx/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_Gx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1228C2-4E65-4EDD-AEF5-8BAA87B9EE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD8C492-F28E-43D1-8014-750B924F853B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="200">
   <si>
     <t>id</t>
   </si>
@@ -530,18 +530,6 @@
     <t>station_name</t>
   </si>
   <si>
-    <t>station_cost</t>
-  </si>
-  <si>
-    <t>distance_to_dn</t>
-  </si>
-  <si>
-    <t>max_chargers</t>
-  </si>
-  <si>
-    <t>man_time</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -572,9 +560,6 @@
     <t>p_max_ssee</t>
   </si>
   <si>
-    <t>max_batteries</t>
-  </si>
-  <si>
     <t>battery_cost</t>
   </si>
   <si>
@@ -630,6 +615,30 @@
   </si>
   <si>
     <t>Bess</t>
+  </si>
+  <si>
+    <t>c_fixed</t>
+  </si>
+  <si>
+    <t>c_bays</t>
+  </si>
+  <si>
+    <t>c_crane</t>
+  </si>
+  <si>
+    <t>c_charger_space</t>
+  </si>
+  <si>
+    <t>c_battery_space</t>
+  </si>
+  <si>
+    <t>max_bays</t>
+  </si>
+  <si>
+    <t>max_batteries_per_bay</t>
+  </si>
+  <si>
+    <t>max_chargers_per_bay</t>
   </si>
 </sst>
 </file>
@@ -1501,36 +1510,36 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" style="23" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" style="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" style="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="23" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5546875" style="24" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.85546875" style="24" customWidth="1"/>
-    <col min="24" max="24" width="18.42578125" style="24" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="24" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.88671875" style="24" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.88671875" style="24" customWidth="1"/>
+    <col min="24" max="24" width="18.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1622,10 +1631,10 @@
         <v>62</v>
       </c>
       <c r="AE1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
@@ -1714,13 +1723,13 @@
         <v>37</v>
       </c>
       <c r="AD2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AE2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31">
         <v>1</v>
       </c>
@@ -1731,7 +1740,7 @@
         <v>161</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>52</v>
@@ -1815,7 +1824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="31">
         <v>2</v>
       </c>
@@ -1826,7 +1835,7 @@
         <v>161</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>52</v>
@@ -1910,7 +1919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="31">
         <v>3</v>
       </c>
@@ -1921,7 +1930,7 @@
         <v>161</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>52</v>
@@ -2005,7 +2014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="31">
         <v>4</v>
       </c>
@@ -2016,7 +2025,7 @@
         <v>161</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>52</v>
@@ -2101,9 +2110,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2112,88 +2121,106 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="B1" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="C1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>163</v>
       </c>
-      <c r="D1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G1" t="s">
-        <v>177</v>
-      </c>
-      <c r="H1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="F2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G2" t="s">
         <v>51</v>
       </c>
       <c r="H2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>169</v>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3">
+        <v>35722</v>
       </c>
       <c r="C3">
-        <v>215756</v>
+        <v>38221</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>16752</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5733</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>4389</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
         <v>1500</v>
       </c>
     </row>
@@ -2206,35 +2233,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1" t="s">
         <v>170</v>
       </c>
-      <c r="C1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>173</v>
-      </c>
-      <c r="F1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G1" t="s">
-        <v>178</v>
       </c>
       <c r="H1" s="13" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2242,7 +2269,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
@@ -2254,18 +2281,18 @@
         <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H2" s="33" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C3">
         <v>42071</v>
@@ -2297,17 +2324,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H152"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.140625" style="69" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="49" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.109375" style="69" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -2333,7 +2360,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="51" t="s">
         <v>3</v>
       </c>
@@ -2359,7 +2386,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="52">
         <v>0</v>
       </c>
@@ -2385,7 +2412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53">
         <v>1</v>
       </c>
@@ -2411,7 +2438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53">
         <v>2</v>
       </c>
@@ -2437,7 +2464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="52">
         <v>3</v>
       </c>
@@ -2463,7 +2490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="53">
         <v>4</v>
       </c>
@@ -2489,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="53">
         <v>5</v>
       </c>
@@ -2515,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52">
         <v>6</v>
       </c>
@@ -2541,7 +2568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="53">
         <v>7</v>
       </c>
@@ -2567,7 +2594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="53">
         <v>8</v>
       </c>
@@ -2593,7 +2620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="52">
         <v>9</v>
       </c>
@@ -2619,7 +2646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="53">
         <v>10</v>
       </c>
@@ -2645,7 +2672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="53">
         <v>11</v>
       </c>
@@ -2671,7 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="53">
         <v>12</v>
       </c>
@@ -2697,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="52">
         <v>13</v>
       </c>
@@ -2723,7 +2750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="53">
         <v>14</v>
       </c>
@@ -2749,7 +2776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="53">
         <v>15</v>
       </c>
@@ -2775,7 +2802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="52">
         <v>16</v>
       </c>
@@ -2801,7 +2828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="53">
         <v>17</v>
       </c>
@@ -2827,7 +2854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="53">
         <v>18</v>
       </c>
@@ -2853,7 +2880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="52">
         <v>19</v>
       </c>
@@ -2879,7 +2906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="53">
         <v>20</v>
       </c>
@@ -2905,7 +2932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="53">
         <v>21</v>
       </c>
@@ -2931,7 +2958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="53">
         <v>22</v>
       </c>
@@ -2957,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="52">
         <v>23</v>
       </c>
@@ -2983,7 +3010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="53">
         <v>24</v>
       </c>
@@ -3009,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="52">
         <v>25</v>
       </c>
@@ -3035,7 +3062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="53">
         <v>26</v>
       </c>
@@ -3061,7 +3088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="53">
         <v>27</v>
       </c>
@@ -3087,7 +3114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="52">
         <v>28</v>
       </c>
@@ -3113,7 +3140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="53">
         <v>29</v>
       </c>
@@ -3139,7 +3166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="53">
         <v>30</v>
       </c>
@@ -3165,7 +3192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="52">
         <v>31</v>
       </c>
@@ -3191,7 +3218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="53">
         <v>32</v>
       </c>
@@ -3217,7 +3244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <v>33</v>
       </c>
@@ -3243,7 +3270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="52">
         <v>34</v>
       </c>
@@ -3269,7 +3296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="53">
         <v>35</v>
       </c>
@@ -3295,7 +3322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="53">
         <v>36</v>
       </c>
@@ -3321,7 +3348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <v>37</v>
       </c>
@@ -3347,7 +3374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="52">
         <v>38</v>
       </c>
@@ -3373,7 +3400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="53">
         <v>39</v>
       </c>
@@ -3399,7 +3426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="53">
         <v>40</v>
       </c>
@@ -3425,7 +3452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="53">
         <v>41</v>
       </c>
@@ -3451,7 +3478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="53">
         <v>42</v>
       </c>
@@ -3477,7 +3504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="53">
         <v>43</v>
       </c>
@@ -3503,7 +3530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="53">
         <v>44</v>
       </c>
@@ -3529,7 +3556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="53">
         <v>45</v>
       </c>
@@ -3555,7 +3582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="53">
         <v>46</v>
       </c>
@@ -3581,7 +3608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="53">
         <v>47</v>
       </c>
@@ -3607,7 +3634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="53">
         <v>48</v>
       </c>
@@ -3633,7 +3660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="53">
         <v>49</v>
       </c>
@@ -3659,7 +3686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="53">
         <v>50</v>
       </c>
@@ -3685,7 +3712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="53">
         <v>51</v>
       </c>
@@ -3711,7 +3738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="53">
         <v>52</v>
       </c>
@@ -3737,7 +3764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="53">
         <v>53</v>
       </c>
@@ -3763,7 +3790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="53">
         <v>54</v>
       </c>
@@ -3789,7 +3816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="53">
         <v>55</v>
       </c>
@@ -3815,7 +3842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="53">
         <v>56</v>
       </c>
@@ -3841,7 +3868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="53">
         <v>57</v>
       </c>
@@ -3867,7 +3894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="53">
         <v>58</v>
       </c>
@@ -3893,7 +3920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="53">
         <v>59</v>
       </c>
@@ -3919,7 +3946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="53">
         <v>60</v>
       </c>
@@ -3945,7 +3972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="53">
         <v>61</v>
       </c>
@@ -3971,7 +3998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="53">
         <v>62</v>
       </c>
@@ -3997,7 +4024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="53">
         <v>63</v>
       </c>
@@ -4023,7 +4050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="53">
         <v>64</v>
       </c>
@@ -4049,7 +4076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="53">
         <v>65</v>
       </c>
@@ -4075,7 +4102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="53">
         <v>66</v>
       </c>
@@ -4101,7 +4128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="53">
         <v>67</v>
       </c>
@@ -4127,7 +4154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="53">
         <v>68</v>
       </c>
@@ -4153,7 +4180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="53">
         <v>69</v>
       </c>
@@ -4179,7 +4206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="53">
         <v>70</v>
       </c>
@@ -4205,7 +4232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="53">
         <v>71</v>
       </c>
@@ -4231,7 +4258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="53">
         <v>72</v>
       </c>
@@ -4257,7 +4284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="53">
         <v>73</v>
       </c>
@@ -4283,7 +4310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="53">
         <v>74</v>
       </c>
@@ -4309,7 +4336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="53">
         <v>75</v>
       </c>
@@ -4335,7 +4362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="53">
         <v>76</v>
       </c>
@@ -4361,7 +4388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="53">
         <v>77</v>
       </c>
@@ -4387,7 +4414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="53">
         <v>78</v>
       </c>
@@ -4413,7 +4440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="53">
         <v>79</v>
       </c>
@@ -4439,7 +4466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="53">
         <v>80</v>
       </c>
@@ -4465,7 +4492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="53">
         <v>81</v>
       </c>
@@ -4491,7 +4518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="53">
         <v>82</v>
       </c>
@@ -4517,7 +4544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="53">
         <v>83</v>
       </c>
@@ -4543,7 +4570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="53">
         <v>84</v>
       </c>
@@ -4569,7 +4596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="53">
         <v>85</v>
       </c>
@@ -4595,7 +4622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="53">
         <v>86</v>
       </c>
@@ -4621,7 +4648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="53">
         <v>87</v>
       </c>
@@ -4647,7 +4674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="53">
         <v>88</v>
       </c>
@@ -4673,7 +4700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="53">
         <v>89</v>
       </c>
@@ -4699,7 +4726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="53">
         <v>90</v>
       </c>
@@ -4725,7 +4752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="53">
         <v>91</v>
       </c>
@@ -4751,7 +4778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="53">
         <v>92</v>
       </c>
@@ -4777,7 +4804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="53">
         <v>93</v>
       </c>
@@ -4803,10 +4830,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="54"/>
       <c r="B98" s="64"/>
       <c r="C98" s="61"/>
@@ -4814,7 +4841,7 @@
       <c r="G98" s="43"/>
       <c r="H98" s="44"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="55"/>
       <c r="B99" s="64"/>
       <c r="C99" s="62"/>
@@ -4822,7 +4849,7 @@
       <c r="G99" s="37"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="56"/>
       <c r="B100" s="64"/>
       <c r="C100" s="62"/>
@@ -4830,7 +4857,7 @@
       <c r="G100" s="37"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="57"/>
       <c r="B101" s="64"/>
       <c r="C101" s="62"/>
@@ -4838,7 +4865,7 @@
       <c r="G101" s="37"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="57"/>
       <c r="B102" s="64"/>
       <c r="C102" s="62"/>
@@ -4846,7 +4873,7 @@
       <c r="G102" s="37"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="57"/>
       <c r="B103" s="64"/>
       <c r="C103" s="62"/>
@@ -4854,7 +4881,7 @@
       <c r="G103" s="37"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="55"/>
       <c r="B104" s="64"/>
       <c r="C104" s="62"/>
@@ -4862,7 +4889,7 @@
       <c r="G104" s="37"/>
       <c r="H104" s="8"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="56"/>
       <c r="B105" s="64"/>
       <c r="C105" s="62"/>
@@ -4870,7 +4897,7 @@
       <c r="G105" s="37"/>
       <c r="H105" s="8"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="57"/>
       <c r="B106" s="64"/>
       <c r="C106" s="62"/>
@@ -4878,7 +4905,7 @@
       <c r="G106" s="37"/>
       <c r="H106" s="8"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="57"/>
       <c r="B107" s="64"/>
       <c r="C107" s="62"/>
@@ -4886,7 +4913,7 @@
       <c r="G107" s="37"/>
       <c r="H107" s="8"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="57"/>
       <c r="B108" s="64"/>
       <c r="C108" s="62"/>
@@ -4894,7 +4921,7 @@
       <c r="G108" s="37"/>
       <c r="H108" s="8"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="55"/>
       <c r="B109" s="64"/>
       <c r="C109" s="62"/>
@@ -4902,7 +4929,7 @@
       <c r="G109" s="37"/>
       <c r="H109" s="8"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="56"/>
       <c r="B110" s="64"/>
       <c r="C110" s="62"/>
@@ -4910,7 +4937,7 @@
       <c r="G110" s="37"/>
       <c r="H110" s="8"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="57"/>
       <c r="B111" s="64"/>
       <c r="C111" s="62"/>
@@ -4918,7 +4945,7 @@
       <c r="G111" s="37"/>
       <c r="H111" s="8"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="57"/>
       <c r="B112" s="64"/>
       <c r="C112" s="62"/>
@@ -4926,7 +4953,7 @@
       <c r="G112" s="37"/>
       <c r="H112" s="8"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="57"/>
       <c r="B113" s="64"/>
       <c r="C113" s="62"/>
@@ -4934,7 +4961,7 @@
       <c r="G113" s="37"/>
       <c r="H113" s="8"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="55"/>
       <c r="B114" s="64"/>
       <c r="C114" s="62"/>
@@ -4942,7 +4969,7 @@
       <c r="G114" s="37"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="56"/>
       <c r="B115" s="64"/>
       <c r="C115" s="62"/>
@@ -4950,7 +4977,7 @@
       <c r="G115" s="37"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="57"/>
       <c r="B116" s="64"/>
       <c r="C116" s="62"/>
@@ -4958,7 +4985,7 @@
       <c r="G116" s="37"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="57"/>
       <c r="B117" s="64"/>
       <c r="C117" s="62"/>
@@ -4966,7 +4993,7 @@
       <c r="G117" s="37"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="57"/>
       <c r="B118" s="64"/>
       <c r="C118" s="62"/>
@@ -4974,7 +5001,7 @@
       <c r="G118" s="37"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="55"/>
       <c r="B119" s="64"/>
       <c r="C119" s="62"/>
@@ -4982,7 +5009,7 @@
       <c r="G119" s="37"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="56"/>
       <c r="B120" s="64"/>
       <c r="C120" s="62"/>
@@ -4990,7 +5017,7 @@
       <c r="G120" s="37"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="57"/>
       <c r="B121" s="64"/>
       <c r="C121" s="62"/>
@@ -4998,7 +5025,7 @@
       <c r="G121" s="37"/>
       <c r="H121" s="8"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="57"/>
       <c r="B122" s="64"/>
       <c r="C122" s="62"/>
@@ -5006,7 +5033,7 @@
       <c r="G122" s="37"/>
       <c r="H122" s="8"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="57"/>
       <c r="B123" s="64"/>
       <c r="C123" s="62"/>
@@ -5014,7 +5041,7 @@
       <c r="G123" s="37"/>
       <c r="H123" s="8"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="55"/>
       <c r="B124" s="64"/>
       <c r="C124" s="62"/>
@@ -5022,7 +5049,7 @@
       <c r="G124" s="37"/>
       <c r="H124" s="8"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="56"/>
       <c r="B125" s="64"/>
       <c r="C125" s="62"/>
@@ -5030,7 +5057,7 @@
       <c r="G125" s="37"/>
       <c r="H125" s="8"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="57"/>
       <c r="B126" s="64"/>
       <c r="C126" s="62"/>
@@ -5038,7 +5065,7 @@
       <c r="G126" s="37"/>
       <c r="H126" s="8"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="57"/>
       <c r="B127" s="64"/>
       <c r="C127" s="62"/>
@@ -5046,7 +5073,7 @@
       <c r="G127" s="37"/>
       <c r="H127" s="8"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="57"/>
       <c r="B128" s="64"/>
       <c r="C128" s="62"/>
@@ -5054,7 +5081,7 @@
       <c r="G128" s="37"/>
       <c r="H128" s="8"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="55"/>
       <c r="B129" s="64"/>
       <c r="C129" s="62"/>
@@ -5062,7 +5089,7 @@
       <c r="G129" s="37"/>
       <c r="H129" s="8"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="56"/>
       <c r="B130" s="64"/>
       <c r="C130" s="62"/>
@@ -5070,7 +5097,7 @@
       <c r="G130" s="37"/>
       <c r="H130" s="8"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="57"/>
       <c r="B131" s="64"/>
       <c r="C131" s="62"/>
@@ -5078,7 +5105,7 @@
       <c r="G131" s="37"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="57"/>
       <c r="B132" s="64"/>
       <c r="C132" s="62"/>
@@ -5086,7 +5113,7 @@
       <c r="G132" s="37"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="57"/>
       <c r="B133" s="64"/>
       <c r="C133" s="62"/>
@@ -5094,7 +5121,7 @@
       <c r="G133" s="37"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="55"/>
       <c r="B134" s="64"/>
       <c r="C134" s="62"/>
@@ -5102,7 +5129,7 @@
       <c r="G134" s="37"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="56"/>
       <c r="B135" s="64"/>
       <c r="C135" s="62"/>
@@ -5110,7 +5137,7 @@
       <c r="G135" s="37"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="57"/>
       <c r="B136" s="64"/>
       <c r="C136" s="62"/>
@@ -5118,7 +5145,7 @@
       <c r="G136" s="37"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="57"/>
       <c r="B137" s="64"/>
       <c r="C137" s="62"/>
@@ -5126,7 +5153,7 @@
       <c r="G137" s="37"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="57"/>
       <c r="B138" s="64"/>
       <c r="C138" s="62"/>
@@ -5134,7 +5161,7 @@
       <c r="G138" s="37"/>
       <c r="H138" s="8"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="55"/>
       <c r="B139" s="64"/>
       <c r="C139" s="62"/>
@@ -5142,7 +5169,7 @@
       <c r="G139" s="37"/>
       <c r="H139" s="8"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="56"/>
       <c r="B140" s="64"/>
       <c r="C140" s="62"/>
@@ -5150,7 +5177,7 @@
       <c r="G140" s="37"/>
       <c r="H140" s="8"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="57"/>
       <c r="B141" s="64"/>
       <c r="C141" s="62"/>
@@ -5158,7 +5185,7 @@
       <c r="G141" s="37"/>
       <c r="H141" s="8"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="57"/>
       <c r="B142" s="64"/>
       <c r="C142" s="62"/>
@@ -5166,7 +5193,7 @@
       <c r="G142" s="37"/>
       <c r="H142" s="8"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="57"/>
       <c r="B143" s="64"/>
       <c r="C143" s="62"/>
@@ -5174,7 +5201,7 @@
       <c r="G143" s="37"/>
       <c r="H143" s="8"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="55"/>
       <c r="B144" s="64"/>
       <c r="C144" s="62"/>
@@ -5182,7 +5209,7 @@
       <c r="G144" s="37"/>
       <c r="H144" s="8"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="56"/>
       <c r="B145" s="64"/>
       <c r="C145" s="62"/>
@@ -5190,7 +5217,7 @@
       <c r="G145" s="37"/>
       <c r="H145" s="8"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="57"/>
       <c r="B146" s="64"/>
       <c r="C146" s="62"/>
@@ -5198,7 +5225,7 @@
       <c r="G146" s="37"/>
       <c r="H146" s="8"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="57"/>
       <c r="B147" s="64"/>
       <c r="C147" s="62"/>
@@ -5206,7 +5233,7 @@
       <c r="G147" s="37"/>
       <c r="H147" s="8"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="57"/>
       <c r="B148" s="64"/>
       <c r="C148" s="62"/>
@@ -5214,7 +5241,7 @@
       <c r="G148" s="37"/>
       <c r="H148" s="8"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="55"/>
       <c r="B149" s="64"/>
       <c r="C149" s="62"/>
@@ -5222,7 +5249,7 @@
       <c r="G149" s="37"/>
       <c r="H149" s="8"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="56"/>
       <c r="B150" s="64"/>
       <c r="C150" s="62"/>
@@ -5230,7 +5257,7 @@
       <c r="G150" s="37"/>
       <c r="H150" s="8"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="57"/>
       <c r="B151" s="64"/>
       <c r="C151" s="62"/>
@@ -5238,7 +5265,7 @@
       <c r="G151" s="37"/>
       <c r="H151" s="8"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="57"/>
       <c r="B152" s="64"/>
       <c r="C152" s="62"/>
@@ -5258,14 +5285,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5276,7 +5303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5287,7 +5314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -5306,9 +5333,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C903B846-9155-4C37-ABE1-59FA4D45CD76}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5316,22 +5343,22 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5342,10 +5369,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -5354,15 +5381,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D3" s="3">
         <v>30.8</v>
@@ -5377,15 +5404,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D4" s="3">
         <v>119</v>
@@ -5408,9 +5435,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387AF5AC-D97C-4B95-B84B-AE3277E9ED2E}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5418,25 +5445,25 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5444,10 +5471,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>34</v>
@@ -5462,12 +5489,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C3" s="4">
         <v>18308</v>

--- a/data/Escenarios_Gx/elmo_data.xlsx
+++ b/data/Escenarios_Gx/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_Gx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2B5433-D3BE-4139-B514-3FBC3CBAD4EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F50D98-6D37-4C46-A5C2-F7CE00860C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="discharge_nodes" sheetId="4" r:id="rId5"/>
     <sheet name="Generators" sheetId="7" r:id="rId6"/>
     <sheet name="Storage" sheetId="8" r:id="rId7"/>
+    <sheet name="BatteryDegradation" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="199">
   <si>
     <t>id</t>
   </si>
@@ -618,6 +619,24 @@
   </si>
   <si>
     <t>max_chargers_per_bay</t>
+  </si>
+  <si>
+    <t>gamma_coef</t>
+  </si>
+  <si>
+    <t>c_bat_replace</t>
+  </si>
+  <si>
+    <t>min_capacity_fraction</t>
+  </si>
+  <si>
+    <t>discount_rate</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>0.1</t>
   </si>
 </sst>
 </file>
@@ -979,7 +998,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1181,6 +1200,21 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1489,36 +1523,37 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" style="23" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" style="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="23" customWidth="1"/>
-    <col min="16" max="16" width="17.109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" style="24" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.88671875" style="24" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.88671875" style="24" customWidth="1"/>
-    <col min="24" max="24" width="18.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.85546875" style="24" customWidth="1"/>
+    <col min="24" max="24" width="18.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1588,26 +1623,26 @@
       <c r="W1" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="X1" s="24" t="s">
+      <c r="X1" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" s="24" t="s">
+      <c r="Y1" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="Z1" s="24" t="s">
+      <c r="Z1" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="24" t="s">
+      <c r="AA1" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
@@ -1677,26 +1712,26 @@
       <c r="W2" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="X2" s="24" t="s">
+      <c r="X2" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="Y2" s="24" t="s">
+      <c r="Y2" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="Z2" s="24" t="s">
+      <c r="Z2" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="AA2" s="24" t="s">
+      <c r="AA2" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" s="27" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="31">
         <v>1</v>
       </c>
@@ -1766,26 +1801,26 @@
       <c r="W3" s="34">
         <v>4</v>
       </c>
-      <c r="X3" s="24">
+      <c r="X3" s="34">
         <v>360</v>
       </c>
-      <c r="Y3" s="24">
+      <c r="Y3" s="34">
         <v>4</v>
       </c>
-      <c r="Z3" s="24">
+      <c r="Z3" s="34">
         <v>353</v>
       </c>
-      <c r="AA3" s="24" t="s">
+      <c r="AA3" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AC3" s="34" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="31">
         <v>2</v>
       </c>
@@ -1855,26 +1890,26 @@
       <c r="W4" s="34">
         <v>4</v>
       </c>
-      <c r="X4" s="24">
+      <c r="X4" s="34">
         <v>360</v>
       </c>
-      <c r="Y4" s="24">
+      <c r="Y4" s="34">
         <v>4</v>
       </c>
-      <c r="Z4" s="24">
+      <c r="Z4" s="34">
         <v>353</v>
       </c>
-      <c r="AA4" s="24" t="s">
+      <c r="AA4" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AB4" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AC4" s="34" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="31">
         <v>3</v>
       </c>
@@ -1944,26 +1979,26 @@
       <c r="W5" s="34">
         <v>4</v>
       </c>
-      <c r="X5" s="24">
+      <c r="X5" s="34">
         <v>360</v>
       </c>
-      <c r="Y5" s="24">
+      <c r="Y5" s="34">
         <v>4</v>
       </c>
-      <c r="Z5" s="24">
+      <c r="Z5" s="34">
         <v>353</v>
       </c>
-      <c r="AA5" s="24" t="s">
+      <c r="AA5" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AB5" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AC5" s="34" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="31">
         <v>4</v>
       </c>
@@ -2033,22 +2068,22 @@
       <c r="W6" s="34">
         <v>4</v>
       </c>
-      <c r="X6" s="24">
+      <c r="X6" s="34">
         <v>360</v>
       </c>
-      <c r="Y6" s="24">
+      <c r="Y6" s="34">
         <v>4</v>
       </c>
-      <c r="Z6" s="24">
+      <c r="Z6" s="34">
         <v>353</v>
       </c>
-      <c r="AA6" s="24" t="s">
+      <c r="AA6" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AB6" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AC6" s="34" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2061,90 +2096,90 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="27" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="27" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="34">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="34">
         <v>35722</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="34">
         <v>38221</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="34">
         <v>5733</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="34">
         <v>2</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="34">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="34">
         <v>1500</v>
       </c>
     </row>
@@ -2157,65 +2192,65 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="27" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="27" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="34">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="34">
         <v>42071</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="34">
         <v>320</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="34">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="34">
         <v>5000</v>
       </c>
     </row>
@@ -2230,17 +2265,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H152"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.109375" style="69" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="49" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.140625" style="69" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -2266,7 +2301,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
         <v>3</v>
       </c>
@@ -2292,7 +2327,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="52">
         <v>0</v>
       </c>
@@ -2318,7 +2353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="53">
         <v>1</v>
       </c>
@@ -2344,7 +2379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="53">
         <v>2</v>
       </c>
@@ -2370,7 +2405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="52">
         <v>3</v>
       </c>
@@ -2396,7 +2431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="53">
         <v>4</v>
       </c>
@@ -2422,7 +2457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="53">
         <v>5</v>
       </c>
@@ -2448,7 +2483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52">
         <v>6</v>
       </c>
@@ -2474,7 +2509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="53">
         <v>7</v>
       </c>
@@ -2500,7 +2535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="53">
         <v>8</v>
       </c>
@@ -2526,7 +2561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="52">
         <v>9</v>
       </c>
@@ -2552,7 +2587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="53">
         <v>10</v>
       </c>
@@ -2578,7 +2613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="53">
         <v>11</v>
       </c>
@@ -2604,7 +2639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="53">
         <v>12</v>
       </c>
@@ -2630,7 +2665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="52">
         <v>13</v>
       </c>
@@ -2656,7 +2691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="53">
         <v>14</v>
       </c>
@@ -2682,7 +2717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="53">
         <v>15</v>
       </c>
@@ -2708,7 +2743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="52">
         <v>16</v>
       </c>
@@ -2734,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="53">
         <v>17</v>
       </c>
@@ -2760,7 +2795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="53">
         <v>18</v>
       </c>
@@ -2786,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="52">
         <v>19</v>
       </c>
@@ -2812,7 +2847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="53">
         <v>20</v>
       </c>
@@ -2838,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="53">
         <v>21</v>
       </c>
@@ -2864,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="53">
         <v>22</v>
       </c>
@@ -2890,7 +2925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="52">
         <v>23</v>
       </c>
@@ -2916,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="53">
         <v>24</v>
       </c>
@@ -2942,7 +2977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="52">
         <v>25</v>
       </c>
@@ -2968,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="53">
         <v>26</v>
       </c>
@@ -2994,7 +3029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="53">
         <v>27</v>
       </c>
@@ -3020,7 +3055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="52">
         <v>28</v>
       </c>
@@ -3046,7 +3081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="53">
         <v>29</v>
       </c>
@@ -3072,7 +3107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="53">
         <v>30</v>
       </c>
@@ -3098,7 +3133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="52">
         <v>31</v>
       </c>
@@ -3124,7 +3159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="53">
         <v>32</v>
       </c>
@@ -3150,7 +3185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="53">
         <v>33</v>
       </c>
@@ -3176,7 +3211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="52">
         <v>34</v>
       </c>
@@ -3202,7 +3237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="53">
         <v>35</v>
       </c>
@@ -3228,7 +3263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="53">
         <v>36</v>
       </c>
@@ -3254,7 +3289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="53">
         <v>37</v>
       </c>
@@ -3280,7 +3315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="52">
         <v>38</v>
       </c>
@@ -3306,7 +3341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="53">
         <v>39</v>
       </c>
@@ -3332,7 +3367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="53">
         <v>40</v>
       </c>
@@ -3358,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="53">
         <v>41</v>
       </c>
@@ -3384,7 +3419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="53">
         <v>42</v>
       </c>
@@ -3410,7 +3445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="53">
         <v>43</v>
       </c>
@@ -3436,7 +3471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="53">
         <v>44</v>
       </c>
@@ -3462,7 +3497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="53">
         <v>45</v>
       </c>
@@ -3488,7 +3523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="53">
         <v>46</v>
       </c>
@@ -3514,7 +3549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="53">
         <v>47</v>
       </c>
@@ -3540,7 +3575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="53">
         <v>48</v>
       </c>
@@ -3566,7 +3601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="53">
         <v>49</v>
       </c>
@@ -3592,7 +3627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="53">
         <v>50</v>
       </c>
@@ -3618,7 +3653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="53">
         <v>51</v>
       </c>
@@ -3644,7 +3679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="53">
         <v>52</v>
       </c>
@@ -3670,7 +3705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="53">
         <v>53</v>
       </c>
@@ -3696,7 +3731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="53">
         <v>54</v>
       </c>
@@ -3722,7 +3757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="53">
         <v>55</v>
       </c>
@@ -3748,7 +3783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="53">
         <v>56</v>
       </c>
@@ -3774,7 +3809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="53">
         <v>57</v>
       </c>
@@ -3800,7 +3835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="53">
         <v>58</v>
       </c>
@@ -3826,7 +3861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="53">
         <v>59</v>
       </c>
@@ -3852,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="53">
         <v>60</v>
       </c>
@@ -3878,7 +3913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="53">
         <v>61</v>
       </c>
@@ -3904,7 +3939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="53">
         <v>62</v>
       </c>
@@ -3930,7 +3965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="53">
         <v>63</v>
       </c>
@@ -3956,7 +3991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="53">
         <v>64</v>
       </c>
@@ -3982,7 +4017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="53">
         <v>65</v>
       </c>
@@ -4008,7 +4043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="53">
         <v>66</v>
       </c>
@@ -4034,7 +4069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="53">
         <v>67</v>
       </c>
@@ -4060,7 +4095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="53">
         <v>68</v>
       </c>
@@ -4086,7 +4121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="53">
         <v>69</v>
       </c>
@@ -4112,7 +4147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="53">
         <v>70</v>
       </c>
@@ -4138,7 +4173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="53">
         <v>71</v>
       </c>
@@ -4164,7 +4199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="53">
         <v>72</v>
       </c>
@@ -4190,7 +4225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="53">
         <v>73</v>
       </c>
@@ -4216,7 +4251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="53">
         <v>74</v>
       </c>
@@ -4242,7 +4277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="53">
         <v>75</v>
       </c>
@@ -4268,7 +4303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="53">
         <v>76</v>
       </c>
@@ -4294,7 +4329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="53">
         <v>77</v>
       </c>
@@ -4320,7 +4355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="53">
         <v>78</v>
       </c>
@@ -4346,7 +4381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="53">
         <v>79</v>
       </c>
@@ -4372,7 +4407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="53">
         <v>80</v>
       </c>
@@ -4398,7 +4433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="53">
         <v>81</v>
       </c>
@@ -4424,7 +4459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="53">
         <v>82</v>
       </c>
@@ -4450,7 +4485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="53">
         <v>83</v>
       </c>
@@ -4476,7 +4511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="53">
         <v>84</v>
       </c>
@@ -4502,7 +4537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="53">
         <v>85</v>
       </c>
@@ -4528,7 +4563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="53">
         <v>86</v>
       </c>
@@ -4554,7 +4589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="53">
         <v>87</v>
       </c>
@@ -4580,7 +4615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="53">
         <v>88</v>
       </c>
@@ -4606,7 +4641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="53">
         <v>89</v>
       </c>
@@ -4632,7 +4667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="53">
         <v>90</v>
       </c>
@@ -4658,7 +4693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="53">
         <v>91</v>
       </c>
@@ -4684,7 +4719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="53">
         <v>92</v>
       </c>
@@ -4710,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="53">
         <v>93</v>
       </c>
@@ -4736,10 +4771,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="53"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97"/>
+      <c r="B97"/>
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97"/>
+      <c r="G97"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="54"/>
       <c r="B98" s="64"/>
       <c r="C98" s="61"/>
@@ -4747,7 +4788,7 @@
       <c r="G98" s="43"/>
       <c r="H98" s="44"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="55"/>
       <c r="B99" s="64"/>
       <c r="C99" s="62"/>
@@ -4755,7 +4796,7 @@
       <c r="G99" s="37"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="56"/>
       <c r="B100" s="64"/>
       <c r="C100" s="62"/>
@@ -4763,7 +4804,7 @@
       <c r="G100" s="37"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="57"/>
       <c r="B101" s="64"/>
       <c r="C101" s="62"/>
@@ -4771,7 +4812,7 @@
       <c r="G101" s="37"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="57"/>
       <c r="B102" s="64"/>
       <c r="C102" s="62"/>
@@ -4779,7 +4820,7 @@
       <c r="G102" s="37"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="57"/>
       <c r="B103" s="64"/>
       <c r="C103" s="62"/>
@@ -4787,7 +4828,7 @@
       <c r="G103" s="37"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="55"/>
       <c r="B104" s="64"/>
       <c r="C104" s="62"/>
@@ -4795,7 +4836,7 @@
       <c r="G104" s="37"/>
       <c r="H104" s="8"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="56"/>
       <c r="B105" s="64"/>
       <c r="C105" s="62"/>
@@ -4803,7 +4844,7 @@
       <c r="G105" s="37"/>
       <c r="H105" s="8"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="57"/>
       <c r="B106" s="64"/>
       <c r="C106" s="62"/>
@@ -4811,7 +4852,7 @@
       <c r="G106" s="37"/>
       <c r="H106" s="8"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="57"/>
       <c r="B107" s="64"/>
       <c r="C107" s="62"/>
@@ -4819,7 +4860,7 @@
       <c r="G107" s="37"/>
       <c r="H107" s="8"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="57"/>
       <c r="B108" s="64"/>
       <c r="C108" s="62"/>
@@ -4827,7 +4868,7 @@
       <c r="G108" s="37"/>
       <c r="H108" s="8"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="55"/>
       <c r="B109" s="64"/>
       <c r="C109" s="62"/>
@@ -4835,7 +4876,7 @@
       <c r="G109" s="37"/>
       <c r="H109" s="8"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="56"/>
       <c r="B110" s="64"/>
       <c r="C110" s="62"/>
@@ -4843,7 +4884,7 @@
       <c r="G110" s="37"/>
       <c r="H110" s="8"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="57"/>
       <c r="B111" s="64"/>
       <c r="C111" s="62"/>
@@ -4851,7 +4892,7 @@
       <c r="G111" s="37"/>
       <c r="H111" s="8"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="57"/>
       <c r="B112" s="64"/>
       <c r="C112" s="62"/>
@@ -4859,7 +4900,7 @@
       <c r="G112" s="37"/>
       <c r="H112" s="8"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="57"/>
       <c r="B113" s="64"/>
       <c r="C113" s="62"/>
@@ -4867,7 +4908,7 @@
       <c r="G113" s="37"/>
       <c r="H113" s="8"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="55"/>
       <c r="B114" s="64"/>
       <c r="C114" s="62"/>
@@ -4875,7 +4916,7 @@
       <c r="G114" s="37"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="56"/>
       <c r="B115" s="64"/>
       <c r="C115" s="62"/>
@@ -4883,7 +4924,7 @@
       <c r="G115" s="37"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="57"/>
       <c r="B116" s="64"/>
       <c r="C116" s="62"/>
@@ -4891,7 +4932,7 @@
       <c r="G116" s="37"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="57"/>
       <c r="B117" s="64"/>
       <c r="C117" s="62"/>
@@ -4899,7 +4940,7 @@
       <c r="G117" s="37"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="57"/>
       <c r="B118" s="64"/>
       <c r="C118" s="62"/>
@@ -4907,7 +4948,7 @@
       <c r="G118" s="37"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="55"/>
       <c r="B119" s="64"/>
       <c r="C119" s="62"/>
@@ -4915,7 +4956,7 @@
       <c r="G119" s="37"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="56"/>
       <c r="B120" s="64"/>
       <c r="C120" s="62"/>
@@ -4923,7 +4964,7 @@
       <c r="G120" s="37"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="57"/>
       <c r="B121" s="64"/>
       <c r="C121" s="62"/>
@@ -4931,7 +4972,7 @@
       <c r="G121" s="37"/>
       <c r="H121" s="8"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="57"/>
       <c r="B122" s="64"/>
       <c r="C122" s="62"/>
@@ -4939,7 +4980,7 @@
       <c r="G122" s="37"/>
       <c r="H122" s="8"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="57"/>
       <c r="B123" s="64"/>
       <c r="C123" s="62"/>
@@ -4947,7 +4988,7 @@
       <c r="G123" s="37"/>
       <c r="H123" s="8"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="55"/>
       <c r="B124" s="64"/>
       <c r="C124" s="62"/>
@@ -4955,7 +4996,7 @@
       <c r="G124" s="37"/>
       <c r="H124" s="8"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="56"/>
       <c r="B125" s="64"/>
       <c r="C125" s="62"/>
@@ -4963,7 +5004,7 @@
       <c r="G125" s="37"/>
       <c r="H125" s="8"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="57"/>
       <c r="B126" s="64"/>
       <c r="C126" s="62"/>
@@ -4971,7 +5012,7 @@
       <c r="G126" s="37"/>
       <c r="H126" s="8"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="57"/>
       <c r="B127" s="64"/>
       <c r="C127" s="62"/>
@@ -4979,7 +5020,7 @@
       <c r="G127" s="37"/>
       <c r="H127" s="8"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="57"/>
       <c r="B128" s="64"/>
       <c r="C128" s="62"/>
@@ -4987,7 +5028,7 @@
       <c r="G128" s="37"/>
       <c r="H128" s="8"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="55"/>
       <c r="B129" s="64"/>
       <c r="C129" s="62"/>
@@ -4995,7 +5036,7 @@
       <c r="G129" s="37"/>
       <c r="H129" s="8"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="56"/>
       <c r="B130" s="64"/>
       <c r="C130" s="62"/>
@@ -5003,7 +5044,7 @@
       <c r="G130" s="37"/>
       <c r="H130" s="8"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="57"/>
       <c r="B131" s="64"/>
       <c r="C131" s="62"/>
@@ -5011,7 +5052,7 @@
       <c r="G131" s="37"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="57"/>
       <c r="B132" s="64"/>
       <c r="C132" s="62"/>
@@ -5019,7 +5060,7 @@
       <c r="G132" s="37"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="57"/>
       <c r="B133" s="64"/>
       <c r="C133" s="62"/>
@@ -5027,7 +5068,7 @@
       <c r="G133" s="37"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="55"/>
       <c r="B134" s="64"/>
       <c r="C134" s="62"/>
@@ -5035,7 +5076,7 @@
       <c r="G134" s="37"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="56"/>
       <c r="B135" s="64"/>
       <c r="C135" s="62"/>
@@ -5043,7 +5084,7 @@
       <c r="G135" s="37"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="57"/>
       <c r="B136" s="64"/>
       <c r="C136" s="62"/>
@@ -5051,7 +5092,7 @@
       <c r="G136" s="37"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="57"/>
       <c r="B137" s="64"/>
       <c r="C137" s="62"/>
@@ -5059,7 +5100,7 @@
       <c r="G137" s="37"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="57"/>
       <c r="B138" s="64"/>
       <c r="C138" s="62"/>
@@ -5067,7 +5108,7 @@
       <c r="G138" s="37"/>
       <c r="H138" s="8"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="55"/>
       <c r="B139" s="64"/>
       <c r="C139" s="62"/>
@@ -5075,7 +5116,7 @@
       <c r="G139" s="37"/>
       <c r="H139" s="8"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="56"/>
       <c r="B140" s="64"/>
       <c r="C140" s="62"/>
@@ -5083,7 +5124,7 @@
       <c r="G140" s="37"/>
       <c r="H140" s="8"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="57"/>
       <c r="B141" s="64"/>
       <c r="C141" s="62"/>
@@ -5091,7 +5132,7 @@
       <c r="G141" s="37"/>
       <c r="H141" s="8"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="57"/>
       <c r="B142" s="64"/>
       <c r="C142" s="62"/>
@@ -5099,7 +5140,7 @@
       <c r="G142" s="37"/>
       <c r="H142" s="8"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="57"/>
       <c r="B143" s="64"/>
       <c r="C143" s="62"/>
@@ -5107,7 +5148,7 @@
       <c r="G143" s="37"/>
       <c r="H143" s="8"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="55"/>
       <c r="B144" s="64"/>
       <c r="C144" s="62"/>
@@ -5115,7 +5156,7 @@
       <c r="G144" s="37"/>
       <c r="H144" s="8"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="56"/>
       <c r="B145" s="64"/>
       <c r="C145" s="62"/>
@@ -5123,7 +5164,7 @@
       <c r="G145" s="37"/>
       <c r="H145" s="8"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="57"/>
       <c r="B146" s="64"/>
       <c r="C146" s="62"/>
@@ -5131,7 +5172,7 @@
       <c r="G146" s="37"/>
       <c r="H146" s="8"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="57"/>
       <c r="B147" s="64"/>
       <c r="C147" s="62"/>
@@ -5139,7 +5180,7 @@
       <c r="G147" s="37"/>
       <c r="H147" s="8"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="57"/>
       <c r="B148" s="64"/>
       <c r="C148" s="62"/>
@@ -5147,7 +5188,7 @@
       <c r="G148" s="37"/>
       <c r="H148" s="8"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="55"/>
       <c r="B149" s="64"/>
       <c r="C149" s="62"/>
@@ -5155,7 +5196,7 @@
       <c r="G149" s="37"/>
       <c r="H149" s="8"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="56"/>
       <c r="B150" s="64"/>
       <c r="C150" s="62"/>
@@ -5163,7 +5204,7 @@
       <c r="G150" s="37"/>
       <c r="H150" s="8"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="57"/>
       <c r="B151" s="64"/>
       <c r="C151" s="62"/>
@@ -5171,7 +5212,7 @@
       <c r="G151" s="37"/>
       <c r="H151" s="8"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="57"/>
       <c r="B152" s="64"/>
       <c r="C152" s="62"/>
@@ -5191,14 +5232,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5209,7 +5250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5220,7 +5261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -5239,9 +5280,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C903B846-9155-4C37-ABE1-59FA4D45CD76}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5264,7 +5305,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5287,7 +5328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -5310,7 +5351,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -5341,9 +5382,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387AF5AC-D97C-4B95-B84B-AE3277E9ED2E}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5369,7 +5413,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5395,7 +5439,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -5419,6 +5463,73 @@
       </c>
       <c r="H3" s="3">
         <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB361D3-2C0F-481F-8505-844CB2F9BDD0}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" s="70" t="s">
+        <v>195</v>
+      </c>
+      <c r="E1" s="72" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" s="70" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" s="72" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="73">
+        <v>1</v>
+      </c>
+      <c r="B3" s="34">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="C3" s="74">
+        <v>79000</v>
+      </c>
+      <c r="D3" s="71">
+        <v>0.8</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
